--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -5046,10 +5046,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117495330</v>
+        <v>117490620</v>
       </c>
       <c r="B41" t="n">
-        <v>78125</v>
+        <v>79521</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,41 +5058,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>412526</v>
+        <v>412636</v>
       </c>
       <c r="R41" t="n">
-        <v>6708022</v>
+        <v>6708175</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,28 +5133,44 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117495325</v>
+        <v>117495330</v>
       </c>
       <c r="B42" t="n">
-        <v>78216</v>
+        <v>78125</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5164,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5188,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412561</v>
+        <v>412526</v>
       </c>
       <c r="R42" t="n">
-        <v>6708064</v>
+        <v>6708022</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5250,10 +5269,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117490620</v>
+        <v>117495325</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>78216</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5262,41 +5281,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412636</v>
+        <v>412561</v>
       </c>
       <c r="R43" t="n">
-        <v>6708175</v>
+        <v>6708064</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5337,34 +5353,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6635,10 +6635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117486703</v>
+        <v>117486531</v>
       </c>
       <c r="B56" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6651,21 +6651,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>412645</v>
+        <v>412681</v>
       </c>
       <c r="R56" t="n">
-        <v>6708155</v>
+        <v>6708233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6741,10 +6741,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117486612</v>
+        <v>117486703</v>
       </c>
       <c r="B57" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6757,21 +6757,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>412692</v>
+        <v>412645</v>
       </c>
       <c r="R57" t="n">
-        <v>6708159</v>
+        <v>6708155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6847,10 +6847,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117486531</v>
+        <v>117486612</v>
       </c>
       <c r="B58" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6863,21 +6863,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6890,10 +6890,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>412681</v>
+        <v>412692</v>
       </c>
       <c r="R58" t="n">
-        <v>6708233</v>
+        <v>6708159</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117495323</v>
+        <v>117487095</v>
       </c>
       <c r="B83" t="n">
-        <v>78217</v>
+        <v>57287</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9550,37 +9550,45 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>412559</v>
+        <v>412695</v>
       </c>
       <c r="R83" t="n">
-        <v>6708064</v>
+        <v>6707998</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9624,22 +9632,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117490817</v>
+        <v>117486636</v>
       </c>
       <c r="B84" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9652,21 +9660,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9675,17 +9683,17 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>412566</v>
+        <v>412677</v>
       </c>
       <c r="R84" t="n">
-        <v>6708147</v>
+        <v>6708150</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9730,22 +9738,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117486636</v>
+        <v>117490129</v>
       </c>
       <c r="B85" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9758,40 +9766,48 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>412677</v>
+        <v>412614</v>
       </c>
       <c r="R85" t="n">
-        <v>6708150</v>
+        <v>6708185</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9833,25 +9849,40 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117490129</v>
+        <v>117495323</v>
       </c>
       <c r="B86" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9864,45 +9895,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>412614</v>
+        <v>412559</v>
       </c>
       <c r="R86" t="n">
-        <v>6708185</v>
+        <v>6708064</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9943,44 +9963,28 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117487095</v>
+        <v>117490817</v>
       </c>
       <c r="B87" t="n">
-        <v>57287</v>
+        <v>78217</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9993,45 +9997,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>412695</v>
+        <v>412566</v>
       </c>
       <c r="R87" t="n">
-        <v>6707998</v>
+        <v>6708147</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10069,18 +10068,19 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -4288,7 +4288,7 @@
         <v>115259343</v>
       </c>
       <c r="B34" t="n">
-        <v>5165</v>
+        <v>5166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117486654</v>
+        <v>117495330</v>
       </c>
       <c r="B39" t="n">
-        <v>78216</v>
+        <v>78125</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4850,40 +4850,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>412621</v>
+        <v>412526</v>
       </c>
       <c r="R39" t="n">
-        <v>6708177</v>
+        <v>6708022</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4921,29 +4918,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117486557</v>
+        <v>117486801</v>
       </c>
       <c r="B40" t="n">
-        <v>90425</v>
+        <v>78506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4952,25 +4948,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3242</v>
+        <v>6434</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,10 +4979,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>412690</v>
+        <v>412596</v>
       </c>
       <c r="R40" t="n">
-        <v>6708211</v>
+        <v>6708194</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5046,10 +5042,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117490620</v>
+        <v>117495318</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>78125</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,44 +5054,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>412636</v>
       </c>
       <c r="R41" t="n">
-        <v>6708175</v>
+        <v>6708031</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5133,44 +5126,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117495330</v>
+        <v>117486832</v>
       </c>
       <c r="B42" t="n">
-        <v>78125</v>
+        <v>78217</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,37 +5160,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412526</v>
+        <v>412569</v>
       </c>
       <c r="R42" t="n">
-        <v>6708022</v>
+        <v>6708173</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5251,28 +5231,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117495325</v>
+        <v>117490236</v>
       </c>
       <c r="B43" t="n">
-        <v>78216</v>
+        <v>6257</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,38 +5262,59 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>105336</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412561</v>
+        <v>412614</v>
       </c>
       <c r="R43" t="n">
-        <v>6708064</v>
+        <v>6708185</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5353,28 +5355,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117490653</v>
+        <v>117486743</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>74592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5387,21 +5390,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5410,17 +5413,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412636</v>
+        <v>412638</v>
       </c>
       <c r="R44" t="n">
-        <v>6708175</v>
+        <v>6708133</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5465,22 +5468,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117495332</v>
+        <v>117490743</v>
       </c>
       <c r="B45" t="n">
-        <v>91962</v>
+        <v>78216</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,34 +5496,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412518</v>
+        <v>412626</v>
       </c>
       <c r="R45" t="n">
-        <v>6708042</v>
+        <v>6708158</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5561,28 +5567,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117490812</v>
+        <v>117490817</v>
       </c>
       <c r="B46" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,21 +5602,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5685,10 +5692,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117486743</v>
+        <v>117495322</v>
       </c>
       <c r="B47" t="n">
-        <v>74592</v>
+        <v>91962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5701,40 +5708,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>2079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>412638</v>
+        <v>412550</v>
       </c>
       <c r="R47" t="n">
-        <v>6708133</v>
+        <v>6708047</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5772,29 +5776,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117486929</v>
+        <v>117495321</v>
       </c>
       <c r="B48" t="n">
-        <v>78216</v>
+        <v>90519</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5807,37 +5810,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>412553</v>
+        <v>412578</v>
       </c>
       <c r="R48" t="n">
-        <v>6708107</v>
+        <v>6708059</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5878,29 +5878,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117486804</v>
+        <v>117490620</v>
       </c>
       <c r="B49" t="n">
-        <v>78216</v>
+        <v>79521</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5909,25 +5908,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5936,17 +5935,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>412596</v>
+        <v>412636</v>
       </c>
       <c r="R49" t="n">
-        <v>6708194</v>
+        <v>6708175</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5988,25 +5987,40 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Iris Elmér, Anton Björk, Carl Teg, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117486935</v>
+        <v>117490653</v>
       </c>
       <c r="B50" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6019,21 +6033,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6042,17 +6056,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>412553</v>
+        <v>412636</v>
       </c>
       <c r="R50" t="n">
-        <v>6708107</v>
+        <v>6708175</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6097,22 +6111,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Iris Elmér, Carl Teg, Anton Björk, August Oljeqvist</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117486983</v>
+        <v>117495335</v>
       </c>
       <c r="B51" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6125,40 +6139,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>412620</v>
+        <v>412668</v>
       </c>
       <c r="R51" t="n">
-        <v>6708033</v>
+        <v>6708050</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6196,29 +6207,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Iris Elmér, Carl Teg, Anton Björk, August Oljeqvist</t>
+          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117490354</v>
+        <v>117495332</v>
       </c>
       <c r="B52" t="n">
-        <v>78216</v>
+        <v>91962</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6231,37 +6241,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>412599</v>
+        <v>412518</v>
       </c>
       <c r="R52" t="n">
-        <v>6708188</v>
+        <v>6708042</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6302,29 +6309,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117486620</v>
+        <v>117486520</v>
       </c>
       <c r="B53" t="n">
-        <v>78216</v>
+        <v>77864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6337,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6364,10 +6370,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>412692</v>
+        <v>412663</v>
       </c>
       <c r="R53" t="n">
-        <v>6708159</v>
+        <v>6708244</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6427,10 +6433,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117486520</v>
+        <v>117486557</v>
       </c>
       <c r="B54" t="n">
-        <v>77864</v>
+        <v>90425</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6443,21 +6449,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6470,10 +6476,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>412663</v>
+        <v>412690</v>
       </c>
       <c r="R54" t="n">
-        <v>6708244</v>
+        <v>6708211</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6533,10 +6539,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117495311</v>
+        <v>117495324</v>
       </c>
       <c r="B55" t="n">
-        <v>90743</v>
+        <v>79098</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6545,25 +6551,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6573,10 +6579,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>412692</v>
+        <v>412559</v>
       </c>
       <c r="R55" t="n">
-        <v>6708190</v>
+        <v>6708061</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6628,17 +6634,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117486531</v>
+        <v>117487095</v>
       </c>
       <c r="B56" t="n">
-        <v>78217</v>
+        <v>57287</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6651,26 +6657,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6678,10 +6689,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>412681</v>
+        <v>412695</v>
       </c>
       <c r="R56" t="n">
-        <v>6708233</v>
+        <v>6707998</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6722,7 +6733,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6741,7 +6751,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117486703</v>
+        <v>117486804</v>
       </c>
       <c r="B57" t="n">
         <v>78216</v>
@@ -6784,10 +6794,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>412645</v>
+        <v>412596</v>
       </c>
       <c r="R57" t="n">
-        <v>6708155</v>
+        <v>6708194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6847,10 +6857,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117486612</v>
+        <v>117486966</v>
       </c>
       <c r="B58" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6863,21 +6873,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6890,10 +6900,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>412692</v>
+        <v>412620</v>
       </c>
       <c r="R58" t="n">
-        <v>6708159</v>
+        <v>6708033</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7059,7 +7069,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117486616</v>
+        <v>117486865</v>
       </c>
       <c r="B60" t="n">
         <v>78217</v>
@@ -7102,10 +7112,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>412692</v>
+        <v>412572</v>
       </c>
       <c r="R60" t="n">
-        <v>6708159</v>
+        <v>6708145</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7165,10 +7175,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117486858</v>
+        <v>117486800</v>
       </c>
       <c r="B61" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7181,21 +7191,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7208,10 +7218,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>412572</v>
+        <v>412596</v>
       </c>
       <c r="R61" t="n">
-        <v>6708145</v>
+        <v>6708194</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7271,10 +7281,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117486801</v>
+        <v>117495314</v>
       </c>
       <c r="B62" t="n">
-        <v>78506</v>
+        <v>78216</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7283,41 +7293,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>412596</v>
+        <v>412645</v>
       </c>
       <c r="R62" t="n">
-        <v>6708194</v>
+        <v>6708117</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7358,29 +7365,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117495333</v>
+        <v>117486584</v>
       </c>
       <c r="B63" t="n">
-        <v>78569</v>
+        <v>78480</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7389,41 +7395,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>412603</v>
+        <v>412649</v>
       </c>
       <c r="R63" t="n">
-        <v>6708003</v>
+        <v>6708206</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7461,28 +7470,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117495321</v>
+        <v>117490812</v>
       </c>
       <c r="B64" t="n">
-        <v>90519</v>
+        <v>78216</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7495,37 +7505,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>412578</v>
+        <v>412566</v>
       </c>
       <c r="R64" t="n">
-        <v>6708059</v>
+        <v>6708147</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7563,28 +7576,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117490236</v>
+        <v>117495317</v>
       </c>
       <c r="B65" t="n">
-        <v>6257</v>
+        <v>82259</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7593,62 +7607,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105336</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>412614</v>
+        <v>412619</v>
       </c>
       <c r="R65" t="n">
-        <v>6708185</v>
+        <v>6708086</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7686,29 +7679,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117495314</v>
+        <v>117486616</v>
       </c>
       <c r="B66" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7721,34 +7713,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>412645</v>
+        <v>412692</v>
       </c>
       <c r="R66" t="n">
-        <v>6708117</v>
+        <v>6708159</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7789,28 +7784,29 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117490477</v>
+        <v>117486929</v>
       </c>
       <c r="B67" t="n">
-        <v>79596</v>
+        <v>78216</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7819,25 +7815,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7846,17 +7842,17 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>412636</v>
+        <v>412553</v>
       </c>
       <c r="R67" t="n">
-        <v>6708175</v>
+        <v>6708107</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7898,40 +7894,25 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117495317</v>
+        <v>117490395</v>
       </c>
       <c r="B68" t="n">
-        <v>82259</v>
+        <v>79561</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7944,37 +7925,52 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>412619</v>
+        <v>412636</v>
       </c>
       <c r="R68" t="n">
-        <v>6708086</v>
+        <v>6708175</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8012,28 +8008,44 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117495313</v>
+        <v>117486935</v>
       </c>
       <c r="B69" t="n">
-        <v>80437</v>
+        <v>78217</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8046,37 +8058,40 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>412652</v>
+        <v>412553</v>
       </c>
       <c r="R69" t="n">
-        <v>6708133</v>
+        <v>6708107</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8114,28 +8129,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117495322</v>
+        <v>117495333</v>
       </c>
       <c r="B70" t="n">
-        <v>91962</v>
+        <v>78569</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8144,25 +8160,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>6450</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8172,10 +8188,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>412550</v>
+        <v>412603</v>
       </c>
       <c r="R70" t="n">
-        <v>6708047</v>
+        <v>6708003</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8227,17 +8243,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117490395</v>
+        <v>117486612</v>
       </c>
       <c r="B71" t="n">
-        <v>79561</v>
+        <v>79098</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8250,52 +8266,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>412636</v>
+        <v>412692</v>
       </c>
       <c r="R71" t="n">
-        <v>6708175</v>
+        <v>6708159</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8337,40 +8341,25 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117495324</v>
+        <v>117490129</v>
       </c>
       <c r="B72" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8383,34 +8372,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>412559</v>
+        <v>412614</v>
       </c>
       <c r="R72" t="n">
-        <v>6708061</v>
+        <v>6708185</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8451,28 +8451,44 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117486865</v>
+        <v>117490477</v>
       </c>
       <c r="B73" t="n">
-        <v>78217</v>
+        <v>79596</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8481,25 +8497,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8508,17 +8524,17 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>412572</v>
+        <v>412636</v>
       </c>
       <c r="R73" t="n">
-        <v>6708145</v>
+        <v>6708175</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8560,22 +8576,37 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117490743</v>
+        <v>117486654</v>
       </c>
       <c r="B74" t="n">
         <v>78216</v>
@@ -8614,17 +8645,17 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>412626</v>
+        <v>412621</v>
       </c>
       <c r="R74" t="n">
-        <v>6708158</v>
+        <v>6708177</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8669,22 +8700,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117486750</v>
+        <v>117486862</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,21 +8728,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8724,10 +8755,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>412638</v>
+        <v>412572</v>
       </c>
       <c r="R75" t="n">
-        <v>6708133</v>
+        <v>6708145</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8787,10 +8818,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117486832</v>
+        <v>117486750</v>
       </c>
       <c r="B76" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8803,21 +8834,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8830,10 +8861,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>412569</v>
+        <v>412638</v>
       </c>
       <c r="R76" t="n">
-        <v>6708173</v>
+        <v>6708133</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8893,10 +8924,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117495315</v>
+        <v>117495325</v>
       </c>
       <c r="B77" t="n">
-        <v>57287</v>
+        <v>78216</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8909,42 +8940,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412654</v>
+        <v>412561</v>
       </c>
       <c r="R77" t="n">
-        <v>6708124</v>
+        <v>6708064</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8979,11 +9002,6 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9001,17 +9019,17 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117486862</v>
+        <v>117486983</v>
       </c>
       <c r="B78" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9024,21 +9042,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9051,10 +9069,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412572</v>
+        <v>412620</v>
       </c>
       <c r="R78" t="n">
-        <v>6708145</v>
+        <v>6708033</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9114,10 +9132,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117486966</v>
+        <v>117486858</v>
       </c>
       <c r="B79" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9130,21 +9148,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9157,10 +9175,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>412620</v>
+        <v>412572</v>
       </c>
       <c r="R79" t="n">
-        <v>6708033</v>
+        <v>6708145</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9213,17 +9231,17 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Iris Elmér, Carl Teg, Anton Björk, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117486584</v>
+        <v>117495311</v>
       </c>
       <c r="B80" t="n">
-        <v>78480</v>
+        <v>90743</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9232,44 +9250,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>412649</v>
+        <v>412692</v>
       </c>
       <c r="R80" t="n">
-        <v>6708206</v>
+        <v>6708190</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9307,29 +9322,28 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117486800</v>
+        <v>117495320</v>
       </c>
       <c r="B81" t="n">
-        <v>78217</v>
+        <v>78514</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9342,37 +9356,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>412596</v>
+        <v>412588</v>
       </c>
       <c r="R81" t="n">
-        <v>6708194</v>
+        <v>6708030</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9413,26 +9424,25 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117495329</v>
+        <v>117495323</v>
       </c>
       <c r="B82" t="n">
         <v>78217</v>
@@ -9472,10 +9482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>412504</v>
+        <v>412559</v>
       </c>
       <c r="R82" t="n">
-        <v>6708038</v>
+        <v>6708064</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9527,17 +9537,17 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117487095</v>
+        <v>117495313</v>
       </c>
       <c r="B83" t="n">
-        <v>57287</v>
+        <v>80437</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9550,45 +9560,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>412695</v>
+        <v>412652</v>
       </c>
       <c r="R83" t="n">
-        <v>6707998</v>
+        <v>6708133</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9632,12 +9634,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9750,10 +9752,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117490129</v>
+        <v>117486531</v>
       </c>
       <c r="B85" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9766,48 +9768,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>412614</v>
+        <v>412681</v>
       </c>
       <c r="R85" t="n">
-        <v>6708185</v>
+        <v>6708233</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9849,40 +9843,25 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117495323</v>
+        <v>117495315</v>
       </c>
       <c r="B86" t="n">
-        <v>78217</v>
+        <v>57287</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9895,34 +9874,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>412559</v>
+        <v>412654</v>
       </c>
       <c r="R86" t="n">
-        <v>6708064</v>
+        <v>6708124</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9957,6 +9944,11 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9974,14 +9966,14 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117490817</v>
+        <v>117495329</v>
       </c>
       <c r="B87" t="n">
         <v>78217</v>
@@ -10015,19 +10007,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>412566</v>
+        <v>412504</v>
       </c>
       <c r="R87" t="n">
-        <v>6708147</v>
+        <v>6708038</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10068,29 +10057,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>Carl Teg, Anton Björk, Iris Elmér, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117495335</v>
+        <v>117490354</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10103,37 +10091,40 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>412668</v>
+        <v>412599</v>
       </c>
       <c r="R88" t="n">
-        <v>6708050</v>
+        <v>6708188</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10171,28 +10162,29 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117495318</v>
+        <v>117486620</v>
       </c>
       <c r="B89" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10205,34 +10197,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>412636</v>
+        <v>412692</v>
       </c>
       <c r="R89" t="n">
-        <v>6708031</v>
+        <v>6708159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10273,28 +10268,29 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117495320</v>
+        <v>117486703</v>
       </c>
       <c r="B90" t="n">
-        <v>78514</v>
+        <v>78216</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10307,34 +10303,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>412588</v>
+        <v>412645</v>
       </c>
       <c r="R90" t="n">
-        <v>6708030</v>
+        <v>6708155</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10375,28 +10374,29 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117763336</v>
+        <v>117768757</v>
       </c>
       <c r="B91" t="n">
-        <v>104929</v>
+        <v>95384</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10405,25 +10405,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>411959</v>
+        <v>412077</v>
       </c>
       <c r="R91" t="n">
-        <v>6707558</v>
+        <v>6707563</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10498,17 +10498,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117768757</v>
+        <v>117773996</v>
       </c>
       <c r="B92" t="n">
-        <v>95384</v>
+        <v>90761</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10521,34 +10521,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bäckelbergssätern, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>412077</v>
+        <v>412088</v>
       </c>
       <c r="R92" t="n">
-        <v>6707563</v>
+        <v>6707397</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10578,49 +10581,40 @@
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Julia Lea Falk, Svea Nikula, Åsa Röstell, Malin Henell, Jonas Göransson, Daniel Söderström, Daniel Hertz Wallin , Carolina Neiker, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117773996</v>
+        <v>117763336</v>
       </c>
       <c r="B93" t="n">
-        <v>90761</v>
+        <v>104929</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10629,41 +10623,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>73</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Bäckelbergssätern, Vrm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>412088</v>
+        <v>411959</v>
       </c>
       <c r="R93" t="n">
-        <v>6707397</v>
+        <v>6707558</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10693,30 +10684,39 @@
           <t>2024-06-14</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-06-14</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Julia Lea Falk, Svea Nikula, Åsa Röstell, Malin Henell, Jonas Göransson, Daniel Söderström, Daniel Hertz Wallin , Carolina Neiker, Carl Teg, Iris Elmér</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117495330</v>
+        <v>117486800</v>
       </c>
       <c r="B39" t="n">
-        <v>78125</v>
+        <v>78219</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4850,37 +4850,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>412526</v>
+        <v>412596</v>
       </c>
       <c r="R39" t="n">
-        <v>6708022</v>
+        <v>6708194</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4918,28 +4921,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117486801</v>
+        <v>117490812</v>
       </c>
       <c r="B40" t="n">
-        <v>78506</v>
+        <v>78218</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,25 +4952,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4975,17 +4979,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>412596</v>
+        <v>412566</v>
       </c>
       <c r="R40" t="n">
-        <v>6708194</v>
+        <v>6708147</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5030,22 +5034,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117495318</v>
+        <v>117486654</v>
       </c>
       <c r="B41" t="n">
-        <v>78125</v>
+        <v>78218</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5058,34 +5062,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>412636</v>
+        <v>412621</v>
       </c>
       <c r="R41" t="n">
-        <v>6708031</v>
+        <v>6708177</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5126,28 +5133,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117486832</v>
+        <v>117486862</v>
       </c>
       <c r="B42" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5160,21 +5168,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5187,10 +5195,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412569</v>
+        <v>412572</v>
       </c>
       <c r="R42" t="n">
-        <v>6708173</v>
+        <v>6708145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5250,10 +5258,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117490236</v>
+        <v>117495335</v>
       </c>
       <c r="B43" t="n">
-        <v>6257</v>
+        <v>78482</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5262,62 +5270,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105336</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412614</v>
+        <v>412668</v>
       </c>
       <c r="R43" t="n">
-        <v>6708185</v>
+        <v>6708050</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5355,29 +5342,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117486743</v>
+        <v>117486612</v>
       </c>
       <c r="B44" t="n">
-        <v>74592</v>
+        <v>79100</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5390,21 +5376,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5417,10 +5403,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412638</v>
+        <v>412692</v>
       </c>
       <c r="R44" t="n">
-        <v>6708133</v>
+        <v>6708159</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5480,10 +5466,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117490743</v>
+        <v>117486520</v>
       </c>
       <c r="B45" t="n">
-        <v>78216</v>
+        <v>77866</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5496,21 +5482,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5519,17 +5505,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412626</v>
+        <v>412663</v>
       </c>
       <c r="R45" t="n">
-        <v>6708158</v>
+        <v>6708244</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5574,22 +5560,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117490817</v>
+        <v>117490129</v>
       </c>
       <c r="B46" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5602,25 +5588,33 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5629,10 +5623,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>412566</v>
+        <v>412614</v>
       </c>
       <c r="R46" t="n">
-        <v>6708147</v>
+        <v>6708185</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5677,6 +5671,21 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -5685,17 +5694,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117495322</v>
+        <v>117490620</v>
       </c>
       <c r="B47" t="n">
-        <v>91962</v>
+        <v>79523</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5704,41 +5713,44 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>412550</v>
+        <v>412636</v>
       </c>
       <c r="R47" t="n">
-        <v>6708047</v>
+        <v>6708175</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5776,28 +5788,44 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117495321</v>
+        <v>117486832</v>
       </c>
       <c r="B48" t="n">
-        <v>90519</v>
+        <v>78219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5810,34 +5838,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>412578</v>
+        <v>412569</v>
       </c>
       <c r="R48" t="n">
-        <v>6708059</v>
+        <v>6708173</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5878,28 +5909,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117490620</v>
+        <v>117487095</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>57288</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5908,44 +5940,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>412636</v>
+        <v>412695</v>
       </c>
       <c r="R49" t="n">
-        <v>6708175</v>
+        <v>6707998</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5983,44 +6020,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Iris Elmér, Anton Björk, Carl Teg, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117490653</v>
+        <v>117495321</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>90521</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6033,40 +6054,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>412636</v>
+        <v>412578</v>
       </c>
       <c r="R50" t="n">
-        <v>6708175</v>
+        <v>6708059</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,29 +6122,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117495335</v>
+        <v>117495313</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>80439</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6139,21 +6156,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6163,13 +6180,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>412668</v>
+        <v>412652</v>
       </c>
       <c r="R51" t="n">
-        <v>6708050</v>
+        <v>6708133</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6218,17 +6235,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117495332</v>
+        <v>117495315</v>
       </c>
       <c r="B52" t="n">
-        <v>91962</v>
+        <v>57288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6241,34 +6258,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>412518</v>
+        <v>412654</v>
       </c>
       <c r="R52" t="n">
-        <v>6708042</v>
+        <v>6708124</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6303,6 +6328,11 @@
           <t>2024-06-02</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6320,17 +6350,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117486520</v>
+        <v>117495324</v>
       </c>
       <c r="B53" t="n">
-        <v>77864</v>
+        <v>79100</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6343,40 +6373,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>412663</v>
+        <v>412559</v>
       </c>
       <c r="R53" t="n">
-        <v>6708244</v>
+        <v>6708061</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6414,29 +6441,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117486557</v>
+        <v>117495318</v>
       </c>
       <c r="B54" t="n">
-        <v>90425</v>
+        <v>78127</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6449,37 +6475,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>412690</v>
+        <v>412636</v>
       </c>
       <c r="R54" t="n">
-        <v>6708211</v>
+        <v>6708031</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6520,29 +6543,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117495324</v>
+        <v>117495311</v>
       </c>
       <c r="B55" t="n">
-        <v>79098</v>
+        <v>90745</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6551,25 +6573,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6579,10 +6601,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>412559</v>
+        <v>412692</v>
       </c>
       <c r="R55" t="n">
-        <v>6708061</v>
+        <v>6708190</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6634,17 +6656,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117487095</v>
+        <v>117495320</v>
       </c>
       <c r="B56" t="n">
-        <v>57287</v>
+        <v>78516</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6657,42 +6679,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>412695</v>
+        <v>412588</v>
       </c>
       <c r="R56" t="n">
-        <v>6707998</v>
+        <v>6708030</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6739,22 +6753,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117486804</v>
+        <v>117486557</v>
       </c>
       <c r="B57" t="n">
-        <v>78216</v>
+        <v>90427</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6767,21 +6781,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6794,10 +6808,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>412596</v>
+        <v>412690</v>
       </c>
       <c r="R57" t="n">
-        <v>6708194</v>
+        <v>6708211</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6857,10 +6871,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117486966</v>
+        <v>117486620</v>
       </c>
       <c r="B58" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6873,21 +6887,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6900,10 +6914,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>412620</v>
+        <v>412692</v>
       </c>
       <c r="R58" t="n">
-        <v>6708033</v>
+        <v>6708159</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6963,10 +6977,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117490696</v>
+        <v>117486966</v>
       </c>
       <c r="B59" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6979,21 +6993,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7002,17 +7016,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>412626</v>
+        <v>412620</v>
       </c>
       <c r="R59" t="n">
-        <v>6708158</v>
+        <v>6708033</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7057,22 +7071,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117486865</v>
+        <v>117490696</v>
       </c>
       <c r="B60" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7108,17 +7122,17 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>412572</v>
+        <v>412626</v>
       </c>
       <c r="R60" t="n">
-        <v>6708145</v>
+        <v>6708158</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7163,22 +7177,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117486800</v>
+        <v>117495322</v>
       </c>
       <c r="B61" t="n">
-        <v>78217</v>
+        <v>91964</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7191,40 +7205,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>412596</v>
+        <v>412550</v>
       </c>
       <c r="R61" t="n">
-        <v>6708194</v>
+        <v>6708047</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7262,29 +7273,28 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117495314</v>
+        <v>117486804</v>
       </c>
       <c r="B62" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7315,16 +7325,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>412645</v>
+        <v>412596</v>
       </c>
       <c r="R62" t="n">
-        <v>6708117</v>
+        <v>6708194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7365,28 +7378,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117486584</v>
+        <v>117486801</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>78508</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7395,25 +7409,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7426,10 +7440,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>412649</v>
+        <v>412596</v>
       </c>
       <c r="R63" t="n">
-        <v>6708206</v>
+        <v>6708194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7489,10 +7503,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117490812</v>
+        <v>117486743</v>
       </c>
       <c r="B64" t="n">
-        <v>78216</v>
+        <v>74594</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7505,21 +7519,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7528,17 +7542,17 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>412566</v>
+        <v>412638</v>
       </c>
       <c r="R64" t="n">
-        <v>6708147</v>
+        <v>6708133</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7583,22 +7597,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117495317</v>
+        <v>117486584</v>
       </c>
       <c r="B65" t="n">
-        <v>82259</v>
+        <v>78482</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7611,34 +7625,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>412619</v>
+        <v>412649</v>
       </c>
       <c r="R65" t="n">
-        <v>6708086</v>
+        <v>6708206</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7679,28 +7696,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117486616</v>
+        <v>117495325</v>
       </c>
       <c r="B66" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7713,40 +7731,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>412692</v>
+        <v>412561</v>
       </c>
       <c r="R66" t="n">
-        <v>6708159</v>
+        <v>6708064</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7784,29 +7799,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117486929</v>
+        <v>117495329</v>
       </c>
       <c r="B67" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7819,40 +7833,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>412553</v>
+        <v>412504</v>
       </c>
       <c r="R67" t="n">
-        <v>6708107</v>
+        <v>6708038</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7890,29 +7901,28 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117490395</v>
+        <v>117495314</v>
       </c>
       <c r="B68" t="n">
-        <v>79561</v>
+        <v>78218</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7925,52 +7935,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>412636</v>
+        <v>412645</v>
       </c>
       <c r="R68" t="n">
-        <v>6708175</v>
+        <v>6708117</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8008,44 +8003,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117486935</v>
+        <v>117486929</v>
       </c>
       <c r="B69" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8058,21 +8037,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8148,10 +8127,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117495333</v>
+        <v>117490817</v>
       </c>
       <c r="B70" t="n">
-        <v>78569</v>
+        <v>78219</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8160,41 +8139,44 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6450</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>412603</v>
+        <v>412566</v>
       </c>
       <c r="R70" t="n">
-        <v>6708003</v>
+        <v>6708147</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8232,28 +8214,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Carl Teg, Iris Elmér, August Oljeqvist, Anton Björk</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117486612</v>
+        <v>117490653</v>
       </c>
       <c r="B71" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8266,21 +8249,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8289,17 +8272,17 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>412692</v>
+        <v>412636</v>
       </c>
       <c r="R71" t="n">
-        <v>6708159</v>
+        <v>6708175</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8344,22 +8327,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117490129</v>
+        <v>117495330</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8372,48 +8355,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>412614</v>
+        <v>412526</v>
       </c>
       <c r="R72" t="n">
-        <v>6708185</v>
+        <v>6708022</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8451,44 +8423,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117490477</v>
+        <v>117490743</v>
       </c>
       <c r="B73" t="n">
-        <v>79596</v>
+        <v>78218</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8497,25 +8453,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8528,10 +8484,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>412636</v>
+        <v>412626</v>
       </c>
       <c r="R73" t="n">
-        <v>6708175</v>
+        <v>6708158</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8576,21 +8532,6 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
@@ -8599,17 +8540,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
+          <t>Iris Elmér, August Oljeqvist, Anton Björk, Carl Teg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117486654</v>
+        <v>117490354</v>
       </c>
       <c r="B74" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8645,17 +8586,17 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>412621</v>
+        <v>412599</v>
       </c>
       <c r="R74" t="n">
-        <v>6708177</v>
+        <v>6708188</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8700,22 +8641,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117486862</v>
+        <v>117486865</v>
       </c>
       <c r="B75" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8728,21 +8669,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8818,10 +8759,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117486750</v>
+        <v>117495317</v>
       </c>
       <c r="B76" t="n">
-        <v>78480</v>
+        <v>82261</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8834,37 +8775,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>412638</v>
+        <v>412619</v>
       </c>
       <c r="R76" t="n">
-        <v>6708133</v>
+        <v>6708086</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8905,29 +8843,28 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117495325</v>
+        <v>117486750</v>
       </c>
       <c r="B77" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8940,37 +8877,40 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412561</v>
+        <v>412638</v>
       </c>
       <c r="R77" t="n">
-        <v>6708064</v>
+        <v>6708133</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9008,28 +8948,29 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117486983</v>
+        <v>117486935</v>
       </c>
       <c r="B78" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9069,10 +9010,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412620</v>
+        <v>412553</v>
       </c>
       <c r="R78" t="n">
-        <v>6708033</v>
+        <v>6708107</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9132,10 +9073,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117486858</v>
+        <v>117490236</v>
       </c>
       <c r="B79" t="n">
-        <v>79098</v>
+        <v>6257</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9144,44 +9085,62 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>105336</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>412572</v>
+        <v>412614</v>
       </c>
       <c r="R79" t="n">
-        <v>6708145</v>
+        <v>6708185</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9226,22 +9185,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117495311</v>
+        <v>117495333</v>
       </c>
       <c r="B80" t="n">
-        <v>90743</v>
+        <v>78571</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9250,25 +9209,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65</v>
+        <v>6450</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9278,13 +9237,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>412692</v>
+        <v>412603</v>
       </c>
       <c r="R80" t="n">
-        <v>6708190</v>
+        <v>6708003</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9333,17 +9292,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117495320</v>
+        <v>117486636</v>
       </c>
       <c r="B81" t="n">
-        <v>78514</v>
+        <v>79100</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9356,34 +9315,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>412588</v>
+        <v>412677</v>
       </c>
       <c r="R81" t="n">
-        <v>6708030</v>
+        <v>6708150</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9424,28 +9386,29 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117495323</v>
+        <v>117486531</v>
       </c>
       <c r="B82" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9476,19 +9439,22 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>412559</v>
+        <v>412681</v>
       </c>
       <c r="R82" t="n">
-        <v>6708064</v>
+        <v>6708233</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9526,28 +9492,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117495313</v>
+        <v>117495332</v>
       </c>
       <c r="B83" t="n">
-        <v>80437</v>
+        <v>91964</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9560,21 +9527,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9584,10 +9551,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>412652</v>
+        <v>412518</v>
       </c>
       <c r="R83" t="n">
-        <v>6708133</v>
+        <v>6708042</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9639,17 +9606,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117486636</v>
+        <v>117490395</v>
       </c>
       <c r="B84" t="n">
-        <v>79098</v>
+        <v>79563</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9662,40 +9629,52 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>412677</v>
+        <v>412636</v>
       </c>
       <c r="R84" t="n">
-        <v>6708150</v>
+        <v>6708175</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9737,25 +9716,40 @@
       <c r="AG84" t="b">
         <v>0</v>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117486531</v>
+        <v>117486858</v>
       </c>
       <c r="B85" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9768,21 +9762,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9795,10 +9789,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>412681</v>
+        <v>412572</v>
       </c>
       <c r="R85" t="n">
-        <v>6708233</v>
+        <v>6708145</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9858,10 +9852,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117495315</v>
+        <v>117486703</v>
       </c>
       <c r="B86" t="n">
-        <v>57287</v>
+        <v>78218</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9874,31 +9868,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9906,13 +9895,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>412654</v>
+        <v>412645</v>
       </c>
       <c r="R86" t="n">
-        <v>6708124</v>
+        <v>6708155</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9944,39 +9933,35 @@
           <t>2024-06-02</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Björk, Carl Teg, Iris Elmér, August Oljeqvist</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117495329</v>
+        <v>117490477</v>
       </c>
       <c r="B87" t="n">
-        <v>78217</v>
+        <v>79598</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9985,38 +9970,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>412504</v>
+        <v>412636</v>
       </c>
       <c r="R87" t="n">
-        <v>6708038</v>
+        <v>6708175</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10057,28 +10045,44 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, Iris Elmér, August Oljeqvist</t>
+          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117490354</v>
+        <v>117486983</v>
       </c>
       <c r="B88" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10091,21 +10095,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10114,17 +10118,17 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>412599</v>
+        <v>412620</v>
       </c>
       <c r="R88" t="n">
-        <v>6708188</v>
+        <v>6708033</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10169,22 +10173,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Carl Teg, August Oljeqvist, Iris Elmér, Anton Björk</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117486620</v>
+        <v>117495323</v>
       </c>
       <c r="B89" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10197,40 +10201,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>412692</v>
+        <v>412559</v>
       </c>
       <c r="R89" t="n">
-        <v>6708159</v>
+        <v>6708064</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10268,29 +10269,28 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117486703</v>
+        <v>117486616</v>
       </c>
       <c r="B90" t="n">
-        <v>78216</v>
+        <v>78219</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10303,21 +10303,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>412645</v>
+        <v>412692</v>
       </c>
       <c r="R90" t="n">
-        <v>6708155</v>
+        <v>6708159</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
         <v>117768757</v>
       </c>
       <c r="B91" t="n">
-        <v>95384</v>
+        <v>95386</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117773996</v>
+        <v>117763336</v>
       </c>
       <c r="B92" t="n">
-        <v>90761</v>
+        <v>104931</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10517,41 +10517,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>73</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Bäckelbergssätern, Vrm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>412088</v>
+        <v>411959</v>
       </c>
       <c r="R92" t="n">
-        <v>6707397</v>
+        <v>6707558</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10581,40 +10578,49 @@
           <t>2024-06-14</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-06-14</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Julia Lea Falk, Svea Nikula, Åsa Röstell, Malin Henell, Jonas Göransson, Daniel Söderström, Daniel Hertz Wallin , Carolina Neiker, Carl Teg, Iris Elmér</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117763336</v>
+        <v>117768740</v>
       </c>
       <c r="B93" t="n">
-        <v>104929</v>
+        <v>90909</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10627,21 +10633,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221144</v>
+        <v>5321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10651,10 +10657,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>411959</v>
+        <v>412077</v>
       </c>
       <c r="R93" t="n">
-        <v>6707558</v>
+        <v>6707563</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10686,7 +10692,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10696,7 +10702,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10716,17 +10722,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117768740</v>
+        <v>117773996</v>
       </c>
       <c r="B94" t="n">
-        <v>90907</v>
+        <v>90763</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10735,38 +10741,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5321</v>
+        <v>73</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bäckelbergssätern, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>412077</v>
+        <v>412088</v>
       </c>
       <c r="R94" t="n">
-        <v>6707563</v>
+        <v>6707397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10796,39 +10805,30 @@
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-06-14</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Julia Lea Falk, Svea Nikula, Åsa Röstell, Malin Henell, Jonas Göransson, Daniel Söderström, Daniel Hertz Wallin , Carolina Neiker, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -4834,10 +4834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117486800</v>
+        <v>117490812</v>
       </c>
       <c r="B39" t="n">
-        <v>78219</v>
+        <v>78218</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4850,21 +4850,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,17 +4873,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>412596</v>
+        <v>412566</v>
       </c>
       <c r="R39" t="n">
-        <v>6708194</v>
+        <v>6708147</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4928,19 +4928,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117490812</v>
+        <v>117486654</v>
       </c>
       <c r="B40" t="n">
         <v>78218</v>
@@ -4979,17 +4979,17 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>412566</v>
+        <v>412621</v>
       </c>
       <c r="R40" t="n">
-        <v>6708147</v>
+        <v>6708177</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5034,19 +5034,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl Teg, Anton Björk, August Oljeqvist, Iris Elmér</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117486654</v>
+        <v>117486862</v>
       </c>
       <c r="B41" t="n">
         <v>78218</v>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>412621</v>
+        <v>412572</v>
       </c>
       <c r="R41" t="n">
-        <v>6708177</v>
+        <v>6708145</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117486862</v>
+        <v>117495335</v>
       </c>
       <c r="B42" t="n">
-        <v>78218</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5168,40 +5168,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412572</v>
+        <v>412668</v>
       </c>
       <c r="R42" t="n">
-        <v>6708145</v>
+        <v>6708050</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5239,29 +5236,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117495335</v>
+        <v>117486612</v>
       </c>
       <c r="B43" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5274,37 +5270,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412668</v>
+        <v>412692</v>
       </c>
       <c r="R43" t="n">
-        <v>6708050</v>
+        <v>6708159</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5342,28 +5341,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117486612</v>
+        <v>117486520</v>
       </c>
       <c r="B44" t="n">
-        <v>79100</v>
+        <v>77866</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5376,21 +5376,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412692</v>
+        <v>412663</v>
       </c>
       <c r="R44" t="n">
-        <v>6708159</v>
+        <v>6708244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117486520</v>
+        <v>117486800</v>
       </c>
       <c r="B45" t="n">
-        <v>77866</v>
+        <v>78219</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412663</v>
+        <v>412596</v>
       </c>
       <c r="R45" t="n">
-        <v>6708244</v>
+        <v>6708194</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117495324</v>
+        <v>117495318</v>
       </c>
       <c r="B53" t="n">
-        <v>79100</v>
+        <v>78127</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6397,13 +6397,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>412559</v>
+        <v>412636</v>
       </c>
       <c r="R53" t="n">
-        <v>6708061</v>
+        <v>6708031</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117495318</v>
+        <v>117495311</v>
       </c>
       <c r="B54" t="n">
-        <v>78127</v>
+        <v>90745</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6499,13 +6499,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>412636</v>
+        <v>412692</v>
       </c>
       <c r="R54" t="n">
-        <v>6708031</v>
+        <v>6708190</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117495311</v>
+        <v>117495320</v>
       </c>
       <c r="B55" t="n">
-        <v>90745</v>
+        <v>78516</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>412692</v>
+        <v>412588</v>
       </c>
       <c r="R55" t="n">
-        <v>6708190</v>
+        <v>6708030</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117495320</v>
+        <v>117495324</v>
       </c>
       <c r="B56" t="n">
-        <v>78516</v>
+        <v>79100</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6679,21 +6679,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6703,13 +6703,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>412588</v>
+        <v>412559</v>
       </c>
       <c r="R56" t="n">
-        <v>6708030</v>
+        <v>6708061</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7083,10 +7083,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117490696</v>
+        <v>117495322</v>
       </c>
       <c r="B60" t="n">
-        <v>78219</v>
+        <v>91964</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7099,40 +7099,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>412626</v>
+        <v>412550</v>
       </c>
       <c r="R60" t="n">
-        <v>6708158</v>
+        <v>6708047</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7170,29 +7167,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117495322</v>
+        <v>117486804</v>
       </c>
       <c r="B61" t="n">
-        <v>91964</v>
+        <v>78218</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7205,37 +7201,40 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>412550</v>
+        <v>412596</v>
       </c>
       <c r="R61" t="n">
-        <v>6708047</v>
+        <v>6708194</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7273,28 +7272,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117486804</v>
+        <v>117486801</v>
       </c>
       <c r="B62" t="n">
-        <v>78218</v>
+        <v>78508</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7303,25 +7303,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7397,10 +7397,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117486801</v>
+        <v>117490696</v>
       </c>
       <c r="B63" t="n">
-        <v>78508</v>
+        <v>78219</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7409,25 +7409,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7436,17 +7436,17 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>412596</v>
+        <v>412626</v>
       </c>
       <c r="R63" t="n">
-        <v>6708194</v>
+        <v>6708158</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7491,12 +7491,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Anton Björk, Carl Teg, Iris Elmér</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8233,10 +8233,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117490653</v>
+        <v>117495330</v>
       </c>
       <c r="B71" t="n">
-        <v>78482</v>
+        <v>78127</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8249,40 +8249,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Nattjärnsskogen, Vrm</t>
+          <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>412636</v>
+        <v>412526</v>
       </c>
       <c r="R71" t="n">
-        <v>6708175</v>
+        <v>6708022</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8320,29 +8317,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Carl Teg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
+          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117495330</v>
+        <v>117490653</v>
       </c>
       <c r="B72" t="n">
-        <v>78127</v>
+        <v>78482</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8355,37 +8351,40 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bäckelberget, Vrm</t>
+          <t>Nattjärnsskogen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>412526</v>
+        <v>412636</v>
       </c>
       <c r="R72" t="n">
-        <v>6708022</v>
+        <v>6708175</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8423,18 +8422,19 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Carl Teg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Björk, August Oljeqvist, Iris Elmér, Carl Teg</t>
+          <t>Anton Björk, Iris Elmér, August Oljeqvist, Carl Teg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054976</v>
+        <v>120054966</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411901</v>
+        <v>411714</v>
       </c>
       <c r="R110" t="n">
-        <v>6707549</v>
+        <v>6707352</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054966</v>
+        <v>120054976</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411714</v>
+        <v>411901</v>
       </c>
       <c r="R111" t="n">
-        <v>6707352</v>
+        <v>6707549</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020795</v>
+        <v>120020723</v>
       </c>
       <c r="B100" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11412,25 +11412,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411952</v>
+        <v>411817</v>
       </c>
       <c r="R100" t="n">
-        <v>6707419</v>
+        <v>6707251</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11490,6 +11490,21 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11506,10 +11521,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020897</v>
+        <v>120020733</v>
       </c>
       <c r="B101" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11537,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11564,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411931</v>
+        <v>412004</v>
       </c>
       <c r="R101" t="n">
-        <v>6707275</v>
+        <v>6707384</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11612,10 +11627,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020748</v>
+        <v>120020731</v>
       </c>
       <c r="B102" t="n">
-        <v>79144</v>
+        <v>79567</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11624,25 +11639,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11655,10 +11670,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R102" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11718,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020889</v>
+        <v>120020748</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11734,21 +11749,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11776,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R103" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11824,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020731</v>
+        <v>120020889</v>
       </c>
       <c r="B104" t="n">
-        <v>79567</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11836,25 +11851,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11867,10 +11882,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>412004</v>
+        <v>411980</v>
       </c>
       <c r="R104" t="n">
-        <v>6707384</v>
+        <v>6707443</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11930,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020753</v>
+        <v>120020832</v>
       </c>
       <c r="B105" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11946,21 +11961,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12036,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020733</v>
+        <v>120020735</v>
       </c>
       <c r="B106" t="n">
-        <v>79607</v>
+        <v>79542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12048,25 +12063,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12142,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020735</v>
+        <v>120020897</v>
       </c>
       <c r="B107" t="n">
-        <v>79542</v>
+        <v>78171</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12154,25 +12169,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12185,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>412004</v>
+        <v>411931</v>
       </c>
       <c r="R107" t="n">
-        <v>6707384</v>
+        <v>6707275</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12248,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020723</v>
+        <v>120020795</v>
       </c>
       <c r="B108" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12260,25 +12275,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12291,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411817</v>
+        <v>411952</v>
       </c>
       <c r="R108" t="n">
-        <v>6707251</v>
+        <v>6707419</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12338,21 +12353,6 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020832</v>
+        <v>120020753</v>
       </c>
       <c r="B109" t="n">
-        <v>78171</v>
+        <v>78262</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054966</v>
+        <v>120054975</v>
       </c>
       <c r="B110" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411714</v>
+        <v>411903</v>
       </c>
       <c r="R110" t="n">
-        <v>6707352</v>
+        <v>6707549</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054976</v>
+        <v>120054966</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411901</v>
+        <v>411714</v>
       </c>
       <c r="R111" t="n">
-        <v>6707549</v>
+        <v>6707352</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054969</v>
+        <v>120054976</v>
       </c>
       <c r="B112" t="n">
-        <v>79479</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12691,44 +12691,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>391</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411805</v>
+        <v>411901</v>
       </c>
       <c r="R112" t="n">
-        <v>6707377</v>
+        <v>6707549</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12766,7 +12763,6 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -12785,10 +12781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054964</v>
+        <v>120054971</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12797,25 +12793,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12825,13 +12821,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411669</v>
+        <v>411826</v>
       </c>
       <c r="R113" t="n">
-        <v>6707329</v>
+        <v>6707438</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12887,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054972</v>
+        <v>120054965</v>
       </c>
       <c r="B114" t="n">
-        <v>95455</v>
+        <v>78262</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12903,21 +12899,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,13 +12923,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411913</v>
+        <v>411707</v>
       </c>
       <c r="R114" t="n">
-        <v>6707396</v>
+        <v>6707356</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054973</v>
+        <v>120054972</v>
       </c>
       <c r="B115" t="n">
-        <v>92030</v>
+        <v>95455</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13005,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,10 +13025,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411943</v>
+        <v>411913</v>
       </c>
       <c r="R115" t="n">
-        <v>6707401</v>
+        <v>6707396</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13091,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054974</v>
+        <v>120054969</v>
       </c>
       <c r="B116" t="n">
-        <v>91840</v>
+        <v>79479</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,41 +13099,44 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>391</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411945</v>
+        <v>411805</v>
       </c>
       <c r="R116" t="n">
-        <v>6707435</v>
+        <v>6707377</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13175,6 +13174,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13193,10 +13193,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054975</v>
+        <v>120054977</v>
       </c>
       <c r="B117" t="n">
-        <v>78262</v>
+        <v>95455</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13209,21 +13209,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411903</v>
+        <v>411907</v>
       </c>
       <c r="R117" t="n">
-        <v>6707549</v>
+        <v>6707588</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054967</v>
+        <v>120054964</v>
       </c>
       <c r="B118" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,25 +13307,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,13 +13335,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411713</v>
+        <v>411669</v>
       </c>
       <c r="R118" t="n">
-        <v>6707349</v>
+        <v>6707329</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054965</v>
+        <v>120054967</v>
       </c>
       <c r="B119" t="n">
-        <v>78262</v>
+        <v>91821</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,25 +13409,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,10 +13437,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411707</v>
+        <v>411713</v>
       </c>
       <c r="R119" t="n">
-        <v>6707356</v>
+        <v>6707349</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054971</v>
+        <v>120054973</v>
       </c>
       <c r="B120" t="n">
-        <v>78262</v>
+        <v>92030</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13515,21 +13515,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,10 +13539,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411826</v>
+        <v>411943</v>
       </c>
       <c r="R120" t="n">
-        <v>6707438</v>
+        <v>6707401</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054977</v>
+        <v>120054974</v>
       </c>
       <c r="B121" t="n">
-        <v>95455</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411907</v>
+        <v>411945</v>
       </c>
       <c r="R121" t="n">
-        <v>6707588</v>
+        <v>6707435</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11191,10 +11191,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119935891</v>
+        <v>119935734</v>
       </c>
       <c r="B98" t="n">
-        <v>86412</v>
+        <v>91883</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3690</v>
+        <v>5448</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411735</v>
+        <v>411881</v>
       </c>
       <c r="R98" t="n">
-        <v>6707169</v>
+        <v>6707228</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11267,6 +11267,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11293,10 +11298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119935734</v>
+        <v>119935891</v>
       </c>
       <c r="B99" t="n">
-        <v>91883</v>
+        <v>86412</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11309,21 +11314,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5448</v>
+        <v>3690</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11333,10 +11338,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411881</v>
+        <v>411735</v>
       </c>
       <c r="R99" t="n">
-        <v>6707228</v>
+        <v>6707169</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11369,11 +11374,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020723</v>
+        <v>120020897</v>
       </c>
       <c r="B100" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11412,25 +11412,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411817</v>
+        <v>411931</v>
       </c>
       <c r="R100" t="n">
-        <v>6707251</v>
+        <v>6707275</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11490,21 +11490,6 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11521,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020733</v>
+        <v>120020795</v>
       </c>
       <c r="B101" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11537,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11564,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R101" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11627,10 +11612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020731</v>
+        <v>120020748</v>
       </c>
       <c r="B102" t="n">
-        <v>79567</v>
+        <v>79144</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11639,25 +11624,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11670,10 +11655,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R102" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11733,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020748</v>
+        <v>120020735</v>
       </c>
       <c r="B103" t="n">
-        <v>79144</v>
+        <v>79542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11745,25 +11730,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11776,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R103" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11839,10 +11824,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020889</v>
+        <v>120020733</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11855,21 +11840,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11882,10 +11867,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411980</v>
+        <v>412004</v>
       </c>
       <c r="R104" t="n">
-        <v>6707443</v>
+        <v>6707384</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12051,10 +12036,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020735</v>
+        <v>120020731</v>
       </c>
       <c r="B106" t="n">
-        <v>79542</v>
+        <v>79567</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12052,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12157,10 +12142,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020897</v>
+        <v>120020723</v>
       </c>
       <c r="B107" t="n">
-        <v>78171</v>
+        <v>90712</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12169,25 +12154,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12185,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411931</v>
+        <v>411817</v>
       </c>
       <c r="R107" t="n">
-        <v>6707275</v>
+        <v>6707251</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12247,6 +12232,21 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020795</v>
+        <v>120020753</v>
       </c>
       <c r="B108" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020753</v>
+        <v>120020889</v>
       </c>
       <c r="B109" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R109" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054975</v>
+        <v>120054976</v>
       </c>
       <c r="B110" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411903</v>
+        <v>411901</v>
       </c>
       <c r="R110" t="n">
         <v>6707549</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054966</v>
+        <v>120054969</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>79479</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12589,41 +12589,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>391</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411714</v>
+        <v>411805</v>
       </c>
       <c r="R111" t="n">
-        <v>6707352</v>
+        <v>6707377</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12661,6 +12664,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12679,10 +12683,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054976</v>
+        <v>120054971</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12695,21 +12699,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,13 +12723,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411901</v>
+        <v>411826</v>
       </c>
       <c r="R112" t="n">
-        <v>6707549</v>
+        <v>6707438</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12781,10 +12785,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054971</v>
+        <v>120054966</v>
       </c>
       <c r="B113" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12797,21 +12801,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12821,13 +12825,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411826</v>
+        <v>411714</v>
       </c>
       <c r="R113" t="n">
-        <v>6707438</v>
+        <v>6707352</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12883,7 +12887,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054965</v>
+        <v>120054975</v>
       </c>
       <c r="B114" t="n">
         <v>78262</v>
@@ -12923,13 +12927,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411707</v>
+        <v>411903</v>
       </c>
       <c r="R114" t="n">
-        <v>6707356</v>
+        <v>6707549</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12985,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054972</v>
+        <v>120054967</v>
       </c>
       <c r="B115" t="n">
-        <v>95455</v>
+        <v>91821</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12997,25 +13001,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>53</v>
+        <v>6055</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13025,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411913</v>
+        <v>411713</v>
       </c>
       <c r="R115" t="n">
-        <v>6707396</v>
+        <v>6707349</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13091,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054969</v>
+        <v>120054972</v>
       </c>
       <c r="B116" t="n">
-        <v>79479</v>
+        <v>95455</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13099,41 +13103,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>391</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411805</v>
+        <v>411913</v>
       </c>
       <c r="R116" t="n">
-        <v>6707377</v>
+        <v>6707396</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13174,7 +13175,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13193,10 +13193,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054977</v>
+        <v>120054973</v>
       </c>
       <c r="B117" t="n">
-        <v>95455</v>
+        <v>92030</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13209,21 +13209,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411907</v>
+        <v>411943</v>
       </c>
       <c r="R117" t="n">
-        <v>6707588</v>
+        <v>6707401</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054967</v>
+        <v>120054974</v>
       </c>
       <c r="B119" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,25 +13409,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,10 +13437,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411713</v>
+        <v>411945</v>
       </c>
       <c r="R119" t="n">
-        <v>6707349</v>
+        <v>6707435</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054973</v>
+        <v>120054965</v>
       </c>
       <c r="B120" t="n">
-        <v>92030</v>
+        <v>78262</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13515,21 +13515,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411943</v>
+        <v>411707</v>
       </c>
       <c r="R120" t="n">
-        <v>6707401</v>
+        <v>6707356</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054974</v>
+        <v>120054977</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>95455</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411945</v>
+        <v>411907</v>
       </c>
       <c r="R121" t="n">
-        <v>6707435</v>
+        <v>6707588</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020795</v>
+        <v>120020832</v>
       </c>
       <c r="B101" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11718,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020735</v>
+        <v>120020723</v>
       </c>
       <c r="B103" t="n">
-        <v>79542</v>
+        <v>90712</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11730,25 +11730,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6457</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>412004</v>
+        <v>411817</v>
       </c>
       <c r="R103" t="n">
-        <v>6707384</v>
+        <v>6707251</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11808,6 +11808,21 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11824,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020733</v>
+        <v>120020889</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11840,21 +11855,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11867,10 +11882,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>412004</v>
+        <v>411980</v>
       </c>
       <c r="R104" t="n">
-        <v>6707384</v>
+        <v>6707443</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11930,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020832</v>
+        <v>120020733</v>
       </c>
       <c r="B105" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11946,21 +11961,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11973,10 +11988,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R105" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12036,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020731</v>
+        <v>120020735</v>
       </c>
       <c r="B106" t="n">
-        <v>79567</v>
+        <v>79542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12052,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12142,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020723</v>
+        <v>120020753</v>
       </c>
       <c r="B107" t="n">
-        <v>90712</v>
+        <v>78262</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12154,25 +12169,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12185,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411817</v>
+        <v>411952</v>
       </c>
       <c r="R107" t="n">
-        <v>6707251</v>
+        <v>6707419</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12232,21 +12247,6 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020753</v>
+        <v>120020795</v>
       </c>
       <c r="B108" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020889</v>
+        <v>120020731</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>79567</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411980</v>
+        <v>412004</v>
       </c>
       <c r="R109" t="n">
-        <v>6707443</v>
+        <v>6707384</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054976</v>
+        <v>120054969</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>79479</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12487,41 +12487,44 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>391</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411901</v>
+        <v>411805</v>
       </c>
       <c r="R110" t="n">
-        <v>6707549</v>
+        <v>6707377</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12559,6 +12562,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12577,10 +12581,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054969</v>
+        <v>120054966</v>
       </c>
       <c r="B111" t="n">
-        <v>79479</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12589,44 +12593,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>391</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411805</v>
+        <v>411714</v>
       </c>
       <c r="R111" t="n">
-        <v>6707377</v>
+        <v>6707352</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12664,7 +12665,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12785,10 +12785,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054966</v>
+        <v>120054972</v>
       </c>
       <c r="B113" t="n">
-        <v>78263</v>
+        <v>95455</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12801,21 +12801,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12825,13 +12825,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411714</v>
+        <v>411913</v>
       </c>
       <c r="R113" t="n">
-        <v>6707352</v>
+        <v>6707396</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12887,10 +12887,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054975</v>
+        <v>120054973</v>
       </c>
       <c r="B114" t="n">
-        <v>78262</v>
+        <v>92030</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12903,21 +12903,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,10 +12927,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411903</v>
+        <v>411943</v>
       </c>
       <c r="R114" t="n">
-        <v>6707549</v>
+        <v>6707401</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12989,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054967</v>
+        <v>120054964</v>
       </c>
       <c r="B115" t="n">
-        <v>91821</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,25 +13001,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411713</v>
+        <v>411669</v>
       </c>
       <c r="R115" t="n">
-        <v>6707349</v>
+        <v>6707329</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13091,10 +13091,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054972</v>
+        <v>120054976</v>
       </c>
       <c r="B116" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13107,21 +13107,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13131,13 +13131,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411913</v>
+        <v>411901</v>
       </c>
       <c r="R116" t="n">
-        <v>6707396</v>
+        <v>6707549</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13193,10 +13193,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054973</v>
+        <v>120054974</v>
       </c>
       <c r="B117" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13205,25 +13205,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13233,13 +13233,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411943</v>
+        <v>411945</v>
       </c>
       <c r="R117" t="n">
-        <v>6707401</v>
+        <v>6707435</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054964</v>
+        <v>120054977</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>95455</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,25 +13307,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,13 +13335,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411669</v>
+        <v>411907</v>
       </c>
       <c r="R118" t="n">
-        <v>6707329</v>
+        <v>6707588</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054974</v>
+        <v>120054975</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,25 +13409,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411945</v>
+        <v>411903</v>
       </c>
       <c r="R119" t="n">
-        <v>6707435</v>
+        <v>6707549</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054977</v>
+        <v>120054967</v>
       </c>
       <c r="B121" t="n">
-        <v>95455</v>
+        <v>91821</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>6055</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411907</v>
+        <v>411713</v>
       </c>
       <c r="R121" t="n">
-        <v>6707588</v>
+        <v>6707349</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054975</v>
+        <v>120054967</v>
       </c>
       <c r="B119" t="n">
-        <v>78262</v>
+        <v>91821</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,25 +13409,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411903</v>
+        <v>411713</v>
       </c>
       <c r="R119" t="n">
-        <v>6707549</v>
+        <v>6707349</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054965</v>
+        <v>120054975</v>
       </c>
       <c r="B120" t="n">
         <v>78262</v>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411707</v>
+        <v>411903</v>
       </c>
       <c r="R120" t="n">
-        <v>6707356</v>
+        <v>6707549</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054967</v>
+        <v>120054965</v>
       </c>
       <c r="B121" t="n">
-        <v>91821</v>
+        <v>78262</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411713</v>
+        <v>411707</v>
       </c>
       <c r="R121" t="n">
-        <v>6707349</v>
+        <v>6707356</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12887,10 +12887,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054973</v>
+        <v>120054964</v>
       </c>
       <c r="B114" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12899,25 +12899,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411943</v>
+        <v>411669</v>
       </c>
       <c r="R114" t="n">
-        <v>6707401</v>
+        <v>6707329</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054964</v>
+        <v>120054973</v>
       </c>
       <c r="B115" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,25 +13001,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411669</v>
+        <v>411943</v>
       </c>
       <c r="R115" t="n">
-        <v>6707329</v>
+        <v>6707401</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054967</v>
+        <v>120054975</v>
       </c>
       <c r="B119" t="n">
-        <v>91821</v>
+        <v>78262</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,25 +13409,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411713</v>
+        <v>411903</v>
       </c>
       <c r="R119" t="n">
-        <v>6707349</v>
+        <v>6707549</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054975</v>
+        <v>120054965</v>
       </c>
       <c r="B120" t="n">
         <v>78262</v>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411903</v>
+        <v>411707</v>
       </c>
       <c r="R120" t="n">
-        <v>6707549</v>
+        <v>6707356</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054965</v>
+        <v>120054967</v>
       </c>
       <c r="B121" t="n">
-        <v>78262</v>
+        <v>91821</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411707</v>
+        <v>411713</v>
       </c>
       <c r="R121" t="n">
-        <v>6707356</v>
+        <v>6707349</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12887,10 +12887,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054964</v>
+        <v>120054973</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12899,25 +12899,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411669</v>
+        <v>411943</v>
       </c>
       <c r="R114" t="n">
-        <v>6707329</v>
+        <v>6707401</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054973</v>
+        <v>120054964</v>
       </c>
       <c r="B115" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,25 +13001,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411943</v>
+        <v>411669</v>
       </c>
       <c r="R115" t="n">
-        <v>6707401</v>
+        <v>6707329</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12887,10 +12887,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054973</v>
+        <v>120054964</v>
       </c>
       <c r="B114" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12899,25 +12899,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,13 +12927,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411943</v>
+        <v>411669</v>
       </c>
       <c r="R114" t="n">
-        <v>6707401</v>
+        <v>6707329</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054964</v>
+        <v>120054973</v>
       </c>
       <c r="B115" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,25 +13001,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411669</v>
+        <v>411943</v>
       </c>
       <c r="R115" t="n">
-        <v>6707329</v>
+        <v>6707401</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11194,7 +11194,7 @@
         <v>119935734</v>
       </c>
       <c r="B98" t="n">
-        <v>91883</v>
+        <v>91901</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>119935891</v>
       </c>
       <c r="B99" t="n">
-        <v>86412</v>
+        <v>86429</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>120020897</v>
       </c>
       <c r="B100" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020832</v>
+        <v>120020753</v>
       </c>
       <c r="B101" t="n">
-        <v>78171</v>
+        <v>78278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11612,10 +11612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020748</v>
+        <v>120020723</v>
       </c>
       <c r="B102" t="n">
-        <v>79144</v>
+        <v>90730</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11624,25 +11624,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411952</v>
+        <v>411817</v>
       </c>
       <c r="R102" t="n">
-        <v>6707419</v>
+        <v>6707251</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,6 +11702,21 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11718,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020723</v>
+        <v>120020832</v>
       </c>
       <c r="B103" t="n">
-        <v>90712</v>
+        <v>78187</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11730,25 +11745,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11776,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411817</v>
+        <v>411952</v>
       </c>
       <c r="R103" t="n">
-        <v>6707251</v>
+        <v>6707419</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11808,21 +11823,6 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11839,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020889</v>
+        <v>120020731</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>79583</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11851,25 +11851,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411980</v>
+        <v>412004</v>
       </c>
       <c r="R104" t="n">
-        <v>6707443</v>
+        <v>6707384</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11945,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020733</v>
+        <v>120020795</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>78279</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R105" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020735</v>
+        <v>120020733</v>
       </c>
       <c r="B106" t="n">
-        <v>79542</v>
+        <v>79623</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12063,25 +12063,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6457</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020753</v>
+        <v>120020889</v>
       </c>
       <c r="B107" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R107" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020795</v>
+        <v>120020748</v>
       </c>
       <c r="B108" t="n">
-        <v>78263</v>
+        <v>79160</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020731</v>
+        <v>120020735</v>
       </c>
       <c r="B109" t="n">
-        <v>79567</v>
+        <v>79558</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054969</v>
+        <v>120054976</v>
       </c>
       <c r="B110" t="n">
-        <v>79479</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12487,44 +12487,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>391</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411805</v>
+        <v>411901</v>
       </c>
       <c r="R110" t="n">
-        <v>6707377</v>
+        <v>6707549</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12562,7 +12559,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12581,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054966</v>
+        <v>120054973</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>92048</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12597,21 +12593,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12621,13 +12617,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411714</v>
+        <v>411943</v>
       </c>
       <c r="R111" t="n">
-        <v>6707352</v>
+        <v>6707401</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12683,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054971</v>
+        <v>120054966</v>
       </c>
       <c r="B112" t="n">
-        <v>78262</v>
+        <v>78279</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12699,21 +12695,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12723,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411826</v>
+        <v>411714</v>
       </c>
       <c r="R112" t="n">
-        <v>6707438</v>
+        <v>6707352</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12785,10 +12781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054972</v>
+        <v>120054977</v>
       </c>
       <c r="B113" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12825,13 +12821,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411913</v>
+        <v>411907</v>
       </c>
       <c r="R113" t="n">
-        <v>6707396</v>
+        <v>6707588</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12887,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054964</v>
+        <v>120054974</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12927,13 +12923,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411669</v>
+        <v>411945</v>
       </c>
       <c r="R114" t="n">
-        <v>6707329</v>
+        <v>6707435</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054973</v>
+        <v>120054975</v>
       </c>
       <c r="B115" t="n">
-        <v>92030</v>
+        <v>78278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13005,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,10 +13025,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411943</v>
+        <v>411903</v>
       </c>
       <c r="R115" t="n">
-        <v>6707401</v>
+        <v>6707549</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13091,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054976</v>
+        <v>120054972</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>95478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13107,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13131,13 +13127,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411901</v>
+        <v>411913</v>
       </c>
       <c r="R116" t="n">
-        <v>6707549</v>
+        <v>6707396</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13193,10 +13189,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054974</v>
+        <v>120054969</v>
       </c>
       <c r="B117" t="n">
-        <v>91840</v>
+        <v>79495</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13205,41 +13201,44 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>391</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411945</v>
+        <v>411805</v>
       </c>
       <c r="R117" t="n">
-        <v>6707435</v>
+        <v>6707377</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13277,6 +13276,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054977</v>
+        <v>120054967</v>
       </c>
       <c r="B118" t="n">
-        <v>95455</v>
+        <v>91839</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,25 +13307,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>53</v>
+        <v>6055</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,10 +13335,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411907</v>
+        <v>411713</v>
       </c>
       <c r="R118" t="n">
-        <v>6707588</v>
+        <v>6707349</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054975</v>
+        <v>120054965</v>
       </c>
       <c r="B119" t="n">
-        <v>78262</v>
+        <v>78278</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13437,13 +13437,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411903</v>
+        <v>411707</v>
       </c>
       <c r="R119" t="n">
-        <v>6707549</v>
+        <v>6707356</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054965</v>
+        <v>120054964</v>
       </c>
       <c r="B120" t="n">
-        <v>78262</v>
+        <v>91858</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13511,25 +13511,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411707</v>
+        <v>411669</v>
       </c>
       <c r="R120" t="n">
-        <v>6707356</v>
+        <v>6707329</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054967</v>
+        <v>120054971</v>
       </c>
       <c r="B121" t="n">
-        <v>91821</v>
+        <v>78278</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,13 +13641,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411713</v>
+        <v>411826</v>
       </c>
       <c r="R121" t="n">
-        <v>6707349</v>
+        <v>6707438</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054976</v>
+        <v>120054966</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411901</v>
+        <v>411714</v>
       </c>
       <c r="R110" t="n">
-        <v>6707549</v>
+        <v>6707352</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054966</v>
+        <v>120054976</v>
       </c>
       <c r="B112" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12695,21 +12695,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,10 +12719,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411714</v>
+        <v>411901</v>
       </c>
       <c r="R112" t="n">
-        <v>6707352</v>
+        <v>6707549</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020897</v>
+        <v>120020748</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411931</v>
+        <v>411952</v>
       </c>
       <c r="R100" t="n">
-        <v>6707275</v>
+        <v>6707419</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020753</v>
+        <v>120020795</v>
       </c>
       <c r="B101" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11733,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020832</v>
+        <v>120020733</v>
       </c>
       <c r="B103" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11749,21 +11749,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R103" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11839,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020731</v>
+        <v>120020735</v>
       </c>
       <c r="B104" t="n">
-        <v>79583</v>
+        <v>79558</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11855,21 +11855,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11945,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020795</v>
+        <v>120020832</v>
       </c>
       <c r="B105" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020733</v>
+        <v>120020753</v>
       </c>
       <c r="B106" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R106" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020889</v>
+        <v>120020897</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411980</v>
+        <v>411931</v>
       </c>
       <c r="R107" t="n">
-        <v>6707443</v>
+        <v>6707275</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020748</v>
+        <v>120020731</v>
       </c>
       <c r="B108" t="n">
-        <v>79160</v>
+        <v>79583</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12275,25 +12275,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R108" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020735</v>
+        <v>120020889</v>
       </c>
       <c r="B109" t="n">
-        <v>79558</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6457</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>412004</v>
+        <v>411980</v>
       </c>
       <c r="R109" t="n">
-        <v>6707384</v>
+        <v>6707443</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054966</v>
+        <v>120054967</v>
       </c>
       <c r="B110" t="n">
-        <v>78279</v>
+        <v>91839</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12487,25 +12487,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6055</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411714</v>
+        <v>411713</v>
       </c>
       <c r="R110" t="n">
-        <v>6707352</v>
+        <v>6707349</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054973</v>
+        <v>120054972</v>
       </c>
       <c r="B111" t="n">
-        <v>92048</v>
+        <v>95478</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411943</v>
+        <v>411913</v>
       </c>
       <c r="R111" t="n">
-        <v>6707401</v>
+        <v>6707396</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054976</v>
+        <v>120054971</v>
       </c>
       <c r="B112" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12695,21 +12695,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411901</v>
+        <v>411826</v>
       </c>
       <c r="R112" t="n">
-        <v>6707549</v>
+        <v>6707438</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12781,10 +12781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054977</v>
+        <v>120054974</v>
       </c>
       <c r="B113" t="n">
-        <v>95478</v>
+        <v>91858</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12793,25 +12793,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12821,10 +12821,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411907</v>
+        <v>411945</v>
       </c>
       <c r="R113" t="n">
-        <v>6707588</v>
+        <v>6707435</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12883,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054974</v>
+        <v>120054973</v>
       </c>
       <c r="B114" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12895,25 +12895,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411945</v>
+        <v>411943</v>
       </c>
       <c r="R114" t="n">
-        <v>6707435</v>
+        <v>6707401</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12985,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054975</v>
+        <v>120054977</v>
       </c>
       <c r="B115" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411903</v>
+        <v>411907</v>
       </c>
       <c r="R115" t="n">
-        <v>6707549</v>
+        <v>6707588</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054972</v>
+        <v>120054976</v>
       </c>
       <c r="B116" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411913</v>
+        <v>411901</v>
       </c>
       <c r="R116" t="n">
-        <v>6707396</v>
+        <v>6707549</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054969</v>
+        <v>120054966</v>
       </c>
       <c r="B117" t="n">
-        <v>79495</v>
+        <v>78279</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13201,44 +13201,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>391</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411805</v>
+        <v>411714</v>
       </c>
       <c r="R117" t="n">
-        <v>6707377</v>
+        <v>6707352</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13276,7 +13273,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13295,10 +13291,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054967</v>
+        <v>120054965</v>
       </c>
       <c r="B118" t="n">
-        <v>91839</v>
+        <v>78278</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,25 +13303,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,10 +13331,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411713</v>
+        <v>411707</v>
       </c>
       <c r="R118" t="n">
-        <v>6707349</v>
+        <v>6707356</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13397,10 +13393,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054965</v>
+        <v>120054969</v>
       </c>
       <c r="B119" t="n">
-        <v>78278</v>
+        <v>79495</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,41 +13405,44 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>391</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411707</v>
+        <v>411805</v>
       </c>
       <c r="R119" t="n">
-        <v>6707356</v>
+        <v>6707377</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13481,6 +13480,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13601,7 +13601,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054971</v>
+        <v>120054975</v>
       </c>
       <c r="B121" t="n">
         <v>78278</v>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411826</v>
+        <v>411903</v>
       </c>
       <c r="R121" t="n">
-        <v>6707438</v>
+        <v>6707549</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12985,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054977</v>
+        <v>120054966</v>
       </c>
       <c r="B115" t="n">
-        <v>95478</v>
+        <v>78279</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411907</v>
+        <v>411714</v>
       </c>
       <c r="R115" t="n">
-        <v>6707588</v>
+        <v>6707352</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054976</v>
+        <v>120054977</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411901</v>
+        <v>411907</v>
       </c>
       <c r="R116" t="n">
-        <v>6707549</v>
+        <v>6707588</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054966</v>
+        <v>120054976</v>
       </c>
       <c r="B117" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13205,21 +13205,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13229,10 +13229,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411714</v>
+        <v>411901</v>
       </c>
       <c r="R117" t="n">
-        <v>6707352</v>
+        <v>6707549</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11191,10 +11191,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119935734</v>
+        <v>119935891</v>
       </c>
       <c r="B98" t="n">
-        <v>91901</v>
+        <v>86429</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5448</v>
+        <v>3690</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411881</v>
+        <v>411735</v>
       </c>
       <c r="R98" t="n">
-        <v>6707228</v>
+        <v>6707169</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11267,11 +11267,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11298,10 +11293,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119935891</v>
+        <v>119935734</v>
       </c>
       <c r="B99" t="n">
-        <v>86429</v>
+        <v>91901</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11314,21 +11309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3690</v>
+        <v>5448</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11338,10 +11333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411735</v>
+        <v>411881</v>
       </c>
       <c r="R99" t="n">
-        <v>6707169</v>
+        <v>6707228</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11374,6 +11369,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020748</v>
+        <v>120020735</v>
       </c>
       <c r="B100" t="n">
-        <v>79160</v>
+        <v>79558</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11412,25 +11412,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6457</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R100" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020795</v>
+        <v>120020897</v>
       </c>
       <c r="B101" t="n">
-        <v>78279</v>
+        <v>78187</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411952</v>
+        <v>411931</v>
       </c>
       <c r="R101" t="n">
-        <v>6707419</v>
+        <v>6707275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11733,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020733</v>
+        <v>120020832</v>
       </c>
       <c r="B103" t="n">
-        <v>79623</v>
+        <v>78187</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11749,21 +11749,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R103" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11839,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020735</v>
+        <v>120020753</v>
       </c>
       <c r="B104" t="n">
-        <v>79558</v>
+        <v>78278</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11851,25 +11851,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R104" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11945,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020832</v>
+        <v>120020733</v>
       </c>
       <c r="B105" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11961,21 +11961,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R105" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020753</v>
+        <v>120020889</v>
       </c>
       <c r="B106" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R106" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020897</v>
+        <v>120020731</v>
       </c>
       <c r="B107" t="n">
-        <v>78187</v>
+        <v>79583</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12169,25 +12169,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411931</v>
+        <v>412004</v>
       </c>
       <c r="R107" t="n">
-        <v>6707275</v>
+        <v>6707384</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020731</v>
+        <v>120020795</v>
       </c>
       <c r="B108" t="n">
-        <v>79583</v>
+        <v>78279</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12275,25 +12275,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R108" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020889</v>
+        <v>120020748</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R109" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054967</v>
+        <v>120054972</v>
       </c>
       <c r="B110" t="n">
-        <v>91839</v>
+        <v>95478</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12487,25 +12487,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6055</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411713</v>
+        <v>411913</v>
       </c>
       <c r="R110" t="n">
-        <v>6707349</v>
+        <v>6707396</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054972</v>
+        <v>120054966</v>
       </c>
       <c r="B111" t="n">
-        <v>95478</v>
+        <v>78279</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12617,13 +12617,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411913</v>
+        <v>411714</v>
       </c>
       <c r="R111" t="n">
-        <v>6707396</v>
+        <v>6707352</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054971</v>
+        <v>120054967</v>
       </c>
       <c r="B112" t="n">
-        <v>78278</v>
+        <v>91839</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12691,25 +12691,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411826</v>
+        <v>411713</v>
       </c>
       <c r="R112" t="n">
-        <v>6707438</v>
+        <v>6707349</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054974</v>
+        <v>120054964</v>
       </c>
       <c r="B113" t="n">
         <v>91858</v>
@@ -12821,13 +12821,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411945</v>
+        <v>411669</v>
       </c>
       <c r="R113" t="n">
-        <v>6707435</v>
+        <v>6707329</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12883,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054973</v>
+        <v>120054977</v>
       </c>
       <c r="B114" t="n">
-        <v>92048</v>
+        <v>95478</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12899,21 +12899,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12923,13 +12923,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411943</v>
+        <v>411907</v>
       </c>
       <c r="R114" t="n">
-        <v>6707401</v>
+        <v>6707588</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12985,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054966</v>
+        <v>120054975</v>
       </c>
       <c r="B115" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411714</v>
+        <v>411903</v>
       </c>
       <c r="R115" t="n">
-        <v>6707352</v>
+        <v>6707549</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054977</v>
+        <v>120054965</v>
       </c>
       <c r="B116" t="n">
-        <v>95478</v>
+        <v>78278</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411907</v>
+        <v>411707</v>
       </c>
       <c r="R116" t="n">
-        <v>6707588</v>
+        <v>6707356</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13291,10 +13291,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054965</v>
+        <v>120054973</v>
       </c>
       <c r="B118" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,21 +13307,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13331,13 +13331,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411707</v>
+        <v>411943</v>
       </c>
       <c r="R118" t="n">
-        <v>6707356</v>
+        <v>6707401</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054964</v>
+        <v>120054971</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13511,25 +13511,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411669</v>
+        <v>411826</v>
       </c>
       <c r="R120" t="n">
-        <v>6707329</v>
+        <v>6707438</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054975</v>
+        <v>120054974</v>
       </c>
       <c r="B121" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,13 +13641,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411903</v>
+        <v>411945</v>
       </c>
       <c r="R121" t="n">
-        <v>6707549</v>
+        <v>6707435</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020889</v>
+        <v>120020731</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>79583</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12063,25 +12063,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411980</v>
+        <v>412004</v>
       </c>
       <c r="R106" t="n">
-        <v>6707443</v>
+        <v>6707384</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020731</v>
+        <v>120020889</v>
       </c>
       <c r="B107" t="n">
-        <v>79583</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12169,25 +12169,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>412004</v>
+        <v>411980</v>
       </c>
       <c r="R107" t="n">
-        <v>6707384</v>
+        <v>6707443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11191,10 +11191,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119935891</v>
+        <v>119935734</v>
       </c>
       <c r="B98" t="n">
-        <v>86429</v>
+        <v>91901</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11207,21 +11207,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3690</v>
+        <v>5448</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>411735</v>
+        <v>411881</v>
       </c>
       <c r="R98" t="n">
-        <v>6707169</v>
+        <v>6707228</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11267,6 +11267,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11293,10 +11298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119935734</v>
+        <v>119935891</v>
       </c>
       <c r="B99" t="n">
-        <v>91901</v>
+        <v>86429</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11309,21 +11314,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5448</v>
+        <v>3690</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11333,10 +11338,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>411881</v>
+        <v>411735</v>
       </c>
       <c r="R99" t="n">
-        <v>6707228</v>
+        <v>6707169</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11369,11 +11374,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Kan det möjligen vara tajgataggsvamp?</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020735</v>
+        <v>120020795</v>
       </c>
       <c r="B100" t="n">
-        <v>79558</v>
+        <v>78279</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11412,25 +11412,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6457</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R100" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020897</v>
+        <v>120020731</v>
       </c>
       <c r="B101" t="n">
-        <v>78187</v>
+        <v>79583</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11518,25 +11518,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411931</v>
+        <v>412004</v>
       </c>
       <c r="R101" t="n">
-        <v>6707275</v>
+        <v>6707384</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11612,10 +11612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020723</v>
+        <v>120020897</v>
       </c>
       <c r="B102" t="n">
-        <v>90730</v>
+        <v>78187</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11624,25 +11624,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411817</v>
+        <v>411931</v>
       </c>
       <c r="R102" t="n">
-        <v>6707251</v>
+        <v>6707275</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11702,21 +11702,6 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11733,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020832</v>
+        <v>120020733</v>
       </c>
       <c r="B103" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11749,21 +11734,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11776,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R103" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11839,10 +11824,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020753</v>
+        <v>120020735</v>
       </c>
       <c r="B104" t="n">
-        <v>78278</v>
+        <v>79558</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11851,25 +11836,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6457</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11882,10 +11867,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R104" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11945,10 +11930,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020733</v>
+        <v>120020723</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>90730</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11957,25 +11942,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11988,10 +11973,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>412004</v>
+        <v>411817</v>
       </c>
       <c r="R105" t="n">
-        <v>6707384</v>
+        <v>6707251</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12035,6 +12020,21 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020731</v>
+        <v>120020748</v>
       </c>
       <c r="B106" t="n">
-        <v>79583</v>
+        <v>79160</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12063,25 +12063,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R106" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020889</v>
+        <v>120020753</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R107" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020795</v>
+        <v>120020889</v>
       </c>
       <c r="B108" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R108" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020748</v>
+        <v>120020832</v>
       </c>
       <c r="B109" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12385,21 +12385,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054972</v>
+        <v>120054971</v>
       </c>
       <c r="B110" t="n">
-        <v>95478</v>
+        <v>78278</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411913</v>
+        <v>411826</v>
       </c>
       <c r="R110" t="n">
-        <v>6707396</v>
+        <v>6707438</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054966</v>
+        <v>120054967</v>
       </c>
       <c r="B111" t="n">
-        <v>78279</v>
+        <v>91839</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12589,25 +12589,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6055</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12617,13 +12617,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411714</v>
+        <v>411713</v>
       </c>
       <c r="R111" t="n">
-        <v>6707352</v>
+        <v>6707349</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054967</v>
+        <v>120054973</v>
       </c>
       <c r="B112" t="n">
-        <v>91839</v>
+        <v>92048</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12691,25 +12691,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6055</v>
+        <v>2079</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411713</v>
+        <v>411943</v>
       </c>
       <c r="R112" t="n">
-        <v>6707349</v>
+        <v>6707401</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12883,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054977</v>
+        <v>120054974</v>
       </c>
       <c r="B114" t="n">
-        <v>95478</v>
+        <v>91858</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12895,25 +12895,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12923,10 +12923,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411907</v>
+        <v>411945</v>
       </c>
       <c r="R114" t="n">
-        <v>6707588</v>
+        <v>6707435</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12985,7 +12985,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054975</v>
+        <v>120054965</v>
       </c>
       <c r="B115" t="n">
         <v>78278</v>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411903</v>
+        <v>411707</v>
       </c>
       <c r="R115" t="n">
-        <v>6707549</v>
+        <v>6707356</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054965</v>
+        <v>120054977</v>
       </c>
       <c r="B116" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411707</v>
+        <v>411907</v>
       </c>
       <c r="R116" t="n">
-        <v>6707356</v>
+        <v>6707588</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054976</v>
+        <v>120054969</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>79495</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13201,41 +13201,44 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>391</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411901</v>
+        <v>411805</v>
       </c>
       <c r="R117" t="n">
-        <v>6707549</v>
+        <v>6707377</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13273,6 +13276,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13291,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054973</v>
+        <v>120054972</v>
       </c>
       <c r="B118" t="n">
-        <v>92048</v>
+        <v>95478</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,21 +13311,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13331,10 +13335,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411943</v>
+        <v>411913</v>
       </c>
       <c r="R118" t="n">
-        <v>6707401</v>
+        <v>6707396</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13393,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054969</v>
+        <v>120054975</v>
       </c>
       <c r="B119" t="n">
-        <v>79495</v>
+        <v>78278</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13405,41 +13409,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>391</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411805</v>
+        <v>411903</v>
       </c>
       <c r="R119" t="n">
-        <v>6707377</v>
+        <v>6707549</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13480,7 +13481,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054971</v>
+        <v>120054966</v>
       </c>
       <c r="B120" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13515,21 +13515,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411826</v>
+        <v>411714</v>
       </c>
       <c r="R120" t="n">
-        <v>6707438</v>
+        <v>6707352</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054974</v>
+        <v>120054976</v>
       </c>
       <c r="B121" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,13 +13641,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411945</v>
+        <v>411901</v>
       </c>
       <c r="R121" t="n">
-        <v>6707435</v>
+        <v>6707549</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020795</v>
+        <v>120020748</v>
       </c>
       <c r="B100" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020731</v>
+        <v>120020753</v>
       </c>
       <c r="B101" t="n">
-        <v>79583</v>
+        <v>78278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11518,25 +11518,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R101" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11612,10 +11612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020897</v>
+        <v>120020735</v>
       </c>
       <c r="B102" t="n">
-        <v>78187</v>
+        <v>79558</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11624,25 +11624,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6457</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11655,10 +11655,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>411931</v>
+        <v>412004</v>
       </c>
       <c r="R102" t="n">
-        <v>6707275</v>
+        <v>6707384</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11718,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020733</v>
+        <v>120020723</v>
       </c>
       <c r="B103" t="n">
-        <v>79623</v>
+        <v>90730</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11730,25 +11730,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>412004</v>
+        <v>411817</v>
       </c>
       <c r="R103" t="n">
-        <v>6707384</v>
+        <v>6707251</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11808,6 +11808,21 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11824,10 +11839,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020735</v>
+        <v>120020897</v>
       </c>
       <c r="B104" t="n">
-        <v>79558</v>
+        <v>78187</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11836,25 +11851,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11867,10 +11882,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>412004</v>
+        <v>411931</v>
       </c>
       <c r="R104" t="n">
-        <v>6707384</v>
+        <v>6707275</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11930,10 +11945,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020723</v>
+        <v>120020733</v>
       </c>
       <c r="B105" t="n">
-        <v>90730</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11942,25 +11957,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11973,10 +11988,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>411817</v>
+        <v>412004</v>
       </c>
       <c r="R105" t="n">
-        <v>6707251</v>
+        <v>6707384</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12020,21 +12035,6 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020748</v>
+        <v>120020889</v>
       </c>
       <c r="B106" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R106" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020753</v>
+        <v>120020795</v>
       </c>
       <c r="B107" t="n">
-        <v>78278</v>
+        <v>78279</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020889</v>
+        <v>120020832</v>
       </c>
       <c r="B108" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12279,21 +12279,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R108" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020832</v>
+        <v>120020731</v>
       </c>
       <c r="B109" t="n">
-        <v>78187</v>
+        <v>79583</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R109" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054971</v>
+        <v>120054972</v>
       </c>
       <c r="B110" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411826</v>
+        <v>411913</v>
       </c>
       <c r="R110" t="n">
-        <v>6707438</v>
+        <v>6707396</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12679,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054973</v>
+        <v>120054964</v>
       </c>
       <c r="B112" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12691,25 +12691,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411943</v>
+        <v>411669</v>
       </c>
       <c r="R112" t="n">
-        <v>6707401</v>
+        <v>6707329</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12781,10 +12781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054964</v>
+        <v>120054976</v>
       </c>
       <c r="B113" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12793,25 +12793,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12821,10 +12821,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411669</v>
+        <v>411901</v>
       </c>
       <c r="R113" t="n">
-        <v>6707329</v>
+        <v>6707549</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12985,7 +12985,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054965</v>
+        <v>120054975</v>
       </c>
       <c r="B115" t="n">
         <v>78278</v>
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411707</v>
+        <v>411903</v>
       </c>
       <c r="R115" t="n">
-        <v>6707356</v>
+        <v>6707549</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054977</v>
+        <v>120054971</v>
       </c>
       <c r="B116" t="n">
-        <v>95478</v>
+        <v>78278</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,21 +13103,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,13 +13127,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411907</v>
+        <v>411826</v>
       </c>
       <c r="R116" t="n">
-        <v>6707588</v>
+        <v>6707438</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054969</v>
+        <v>120054966</v>
       </c>
       <c r="B117" t="n">
-        <v>79495</v>
+        <v>78279</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13201,44 +13201,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>391</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411805</v>
+        <v>411714</v>
       </c>
       <c r="R117" t="n">
-        <v>6707377</v>
+        <v>6707352</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13276,7 +13273,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13295,10 +13291,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054972</v>
+        <v>120054973</v>
       </c>
       <c r="B118" t="n">
-        <v>95478</v>
+        <v>92048</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13311,21 +13307,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,10 +13331,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411913</v>
+        <v>411943</v>
       </c>
       <c r="R118" t="n">
-        <v>6707396</v>
+        <v>6707401</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13397,10 +13393,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054975</v>
+        <v>120054969</v>
       </c>
       <c r="B119" t="n">
-        <v>78278</v>
+        <v>79495</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13409,38 +13405,41 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>391</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411903</v>
+        <v>411805</v>
       </c>
       <c r="R119" t="n">
-        <v>6707549</v>
+        <v>6707377</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13481,6 +13480,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054966</v>
+        <v>120054965</v>
       </c>
       <c r="B120" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13515,21 +13515,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411714</v>
+        <v>411707</v>
       </c>
       <c r="R120" t="n">
-        <v>6707352</v>
+        <v>6707356</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054976</v>
+        <v>120054977</v>
       </c>
       <c r="B121" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13617,21 +13617,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,13 +13641,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411901</v>
+        <v>411907</v>
       </c>
       <c r="R121" t="n">
-        <v>6707549</v>
+        <v>6707588</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020753</v>
+        <v>120020723</v>
       </c>
       <c r="B101" t="n">
-        <v>78278</v>
+        <v>90730</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11518,25 +11518,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411952</v>
+        <v>411817</v>
       </c>
       <c r="R101" t="n">
-        <v>6707419</v>
+        <v>6707251</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11596,6 +11596,21 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11612,10 +11627,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020735</v>
+        <v>120020753</v>
       </c>
       <c r="B102" t="n">
-        <v>79558</v>
+        <v>78278</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11624,25 +11639,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6457</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11655,10 +11670,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R102" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11718,10 +11733,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020723</v>
+        <v>120020735</v>
       </c>
       <c r="B103" t="n">
-        <v>90730</v>
+        <v>79558</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11730,25 +11745,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>6457</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11776,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411817</v>
+        <v>412004</v>
       </c>
       <c r="R103" t="n">
-        <v>6707251</v>
+        <v>6707384</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11808,21 +11823,6 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020889</v>
+        <v>120020795</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R106" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020795</v>
+        <v>120020889</v>
       </c>
       <c r="B107" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R107" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020748</v>
+        <v>120020897</v>
       </c>
       <c r="B100" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411952</v>
+        <v>411931</v>
       </c>
       <c r="R100" t="n">
-        <v>6707419</v>
+        <v>6707275</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020723</v>
+        <v>120020753</v>
       </c>
       <c r="B101" t="n">
-        <v>90730</v>
+        <v>78278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11518,25 +11518,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411817</v>
+        <v>411952</v>
       </c>
       <c r="R101" t="n">
-        <v>6707251</v>
+        <v>6707419</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11596,21 +11596,6 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11627,10 +11612,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120020753</v>
+        <v>120020748</v>
       </c>
       <c r="B102" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11643,21 +11628,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11733,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020735</v>
+        <v>120020832</v>
       </c>
       <c r="B103" t="n">
-        <v>79558</v>
+        <v>78187</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11745,25 +11730,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11776,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R103" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11839,10 +11824,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020897</v>
+        <v>120020723</v>
       </c>
       <c r="B104" t="n">
-        <v>78187</v>
+        <v>90730</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11851,25 +11836,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11882,10 +11867,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411931</v>
+        <v>411817</v>
       </c>
       <c r="R104" t="n">
-        <v>6707275</v>
+        <v>6707251</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11929,6 +11914,21 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12051,10 +12051,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020795</v>
+        <v>120020889</v>
       </c>
       <c r="B106" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12067,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R106" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12157,10 +12157,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120020889</v>
+        <v>120020735</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>79558</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12169,25 +12169,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6457</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12200,10 +12200,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>411980</v>
+        <v>412004</v>
       </c>
       <c r="R107" t="n">
-        <v>6707443</v>
+        <v>6707384</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12263,10 +12263,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020832</v>
+        <v>120020731</v>
       </c>
       <c r="B108" t="n">
-        <v>78187</v>
+        <v>79583</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12275,25 +12275,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>411952</v>
+        <v>412004</v>
       </c>
       <c r="R108" t="n">
-        <v>6707419</v>
+        <v>6707384</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12369,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020731</v>
+        <v>120020795</v>
       </c>
       <c r="B109" t="n">
-        <v>79583</v>
+        <v>78279</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12381,25 +12381,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R109" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054972</v>
+        <v>120054975</v>
       </c>
       <c r="B110" t="n">
-        <v>95478</v>
+        <v>78278</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12491,21 +12491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,10 +12515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411913</v>
+        <v>411903</v>
       </c>
       <c r="R110" t="n">
-        <v>6707396</v>
+        <v>6707549</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054967</v>
+        <v>120054969</v>
       </c>
       <c r="B111" t="n">
-        <v>91839</v>
+        <v>79495</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12589,41 +12589,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6055</v>
+        <v>391</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411713</v>
+        <v>411805</v>
       </c>
       <c r="R111" t="n">
-        <v>6707349</v>
+        <v>6707377</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12661,6 +12664,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12679,10 +12683,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054964</v>
+        <v>120054976</v>
       </c>
       <c r="B112" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12691,25 +12695,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12719,10 +12723,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411669</v>
+        <v>411901</v>
       </c>
       <c r="R112" t="n">
-        <v>6707329</v>
+        <v>6707549</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12781,10 +12785,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054976</v>
+        <v>120054972</v>
       </c>
       <c r="B113" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12797,21 +12801,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12821,13 +12825,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411901</v>
+        <v>411913</v>
       </c>
       <c r="R113" t="n">
-        <v>6707549</v>
+        <v>6707396</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12883,10 +12887,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054974</v>
+        <v>120054966</v>
       </c>
       <c r="B114" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12895,25 +12899,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12923,13 +12927,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411945</v>
+        <v>411714</v>
       </c>
       <c r="R114" t="n">
-        <v>6707435</v>
+        <v>6707352</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12985,10 +12989,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054975</v>
+        <v>120054977</v>
       </c>
       <c r="B115" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13001,21 +13005,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13025,13 +13029,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411903</v>
+        <v>411907</v>
       </c>
       <c r="R115" t="n">
-        <v>6707549</v>
+        <v>6707588</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13087,10 +13091,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054971</v>
+        <v>120054967</v>
       </c>
       <c r="B116" t="n">
-        <v>78278</v>
+        <v>91839</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13099,25 +13103,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>6055</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13127,13 +13131,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411826</v>
+        <v>411713</v>
       </c>
       <c r="R116" t="n">
-        <v>6707438</v>
+        <v>6707349</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13189,10 +13193,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054966</v>
+        <v>120054973</v>
       </c>
       <c r="B117" t="n">
-        <v>78279</v>
+        <v>92048</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13205,21 +13209,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13229,13 +13233,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411714</v>
+        <v>411943</v>
       </c>
       <c r="R117" t="n">
-        <v>6707352</v>
+        <v>6707401</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13291,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054973</v>
+        <v>120054965</v>
       </c>
       <c r="B118" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13307,21 +13311,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13331,13 +13335,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411943</v>
+        <v>411707</v>
       </c>
       <c r="R118" t="n">
-        <v>6707401</v>
+        <v>6707356</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13393,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054969</v>
+        <v>120054971</v>
       </c>
       <c r="B119" t="n">
-        <v>79495</v>
+        <v>78278</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13405,41 +13409,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>391</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411805</v>
+        <v>411826</v>
       </c>
       <c r="R119" t="n">
-        <v>6707377</v>
+        <v>6707438</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13480,7 +13481,6 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054965</v>
+        <v>120054974</v>
       </c>
       <c r="B120" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13511,25 +13511,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,10 +13539,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411707</v>
+        <v>411945</v>
       </c>
       <c r="R120" t="n">
-        <v>6707356</v>
+        <v>6707435</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054977</v>
+        <v>120054964</v>
       </c>
       <c r="B121" t="n">
-        <v>95478</v>
+        <v>91858</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,13 +13641,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411907</v>
+        <v>411669</v>
       </c>
       <c r="R121" t="n">
-        <v>6707588</v>
+        <v>6707329</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -11400,10 +11400,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120020897</v>
+        <v>120020733</v>
       </c>
       <c r="B100" t="n">
-        <v>78187</v>
+        <v>79623</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11416,21 +11416,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>411931</v>
+        <v>412004</v>
       </c>
       <c r="R100" t="n">
-        <v>6707275</v>
+        <v>6707384</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11506,10 +11506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120020753</v>
+        <v>120020897</v>
       </c>
       <c r="B101" t="n">
-        <v>78278</v>
+        <v>78187</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11522,21 +11522,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>411952</v>
+        <v>411931</v>
       </c>
       <c r="R101" t="n">
-        <v>6707419</v>
+        <v>6707275</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11718,10 +11718,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120020832</v>
+        <v>120020889</v>
       </c>
       <c r="B103" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11734,21 +11734,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>411952</v>
+        <v>411980</v>
       </c>
       <c r="R103" t="n">
-        <v>6707419</v>
+        <v>6707443</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11824,10 +11824,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120020723</v>
+        <v>120020795</v>
       </c>
       <c r="B104" t="n">
-        <v>90730</v>
+        <v>78279</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11836,25 +11836,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>411817</v>
+        <v>411952</v>
       </c>
       <c r="R104" t="n">
-        <v>6707251</v>
+        <v>6707419</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11914,21 +11914,6 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11945,10 +11930,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120020733</v>
+        <v>120020731</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>79583</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11957,25 +11942,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12051,10 +12036,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120020889</v>
+        <v>120020832</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12067,21 +12052,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12094,10 +12079,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>411980</v>
+        <v>411952</v>
       </c>
       <c r="R106" t="n">
-        <v>6707443</v>
+        <v>6707419</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12263,10 +12248,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120020731</v>
+        <v>120020753</v>
       </c>
       <c r="B108" t="n">
-        <v>79583</v>
+        <v>78278</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12275,25 +12260,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12306,10 +12291,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>412004</v>
+        <v>411952</v>
       </c>
       <c r="R108" t="n">
-        <v>6707384</v>
+        <v>6707419</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12369,10 +12354,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120020795</v>
+        <v>120020723</v>
       </c>
       <c r="B109" t="n">
-        <v>78279</v>
+        <v>90730</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12381,25 +12366,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12412,10 +12397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>411952</v>
+        <v>411817</v>
       </c>
       <c r="R109" t="n">
-        <v>6707419</v>
+        <v>6707251</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12459,6 +12444,21 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12475,10 +12475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120054975</v>
+        <v>120054964</v>
       </c>
       <c r="B110" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12487,25 +12487,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12515,13 +12515,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>411903</v>
+        <v>411669</v>
       </c>
       <c r="R110" t="n">
-        <v>6707549</v>
+        <v>6707329</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120054969</v>
+        <v>120054974</v>
       </c>
       <c r="B111" t="n">
-        <v>79495</v>
+        <v>91858</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12589,44 +12589,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>391</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grynig gelélav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Collema subflaccidum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>411805</v>
+        <v>411945</v>
       </c>
       <c r="R111" t="n">
-        <v>6707377</v>
+        <v>6707435</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12664,7 +12661,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12683,10 +12679,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120054976</v>
+        <v>120054965</v>
       </c>
       <c r="B112" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12699,21 +12695,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12723,13 +12719,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>411901</v>
+        <v>411707</v>
       </c>
       <c r="R112" t="n">
-        <v>6707549</v>
+        <v>6707356</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12785,10 +12781,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120054972</v>
+        <v>120054976</v>
       </c>
       <c r="B113" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12801,21 +12797,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12825,13 +12821,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>411913</v>
+        <v>411901</v>
       </c>
       <c r="R113" t="n">
-        <v>6707396</v>
+        <v>6707549</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12887,10 +12883,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120054966</v>
+        <v>120054977</v>
       </c>
       <c r="B114" t="n">
-        <v>78279</v>
+        <v>95478</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12903,21 +12899,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12927,13 +12923,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>411714</v>
+        <v>411907</v>
       </c>
       <c r="R114" t="n">
-        <v>6707352</v>
+        <v>6707588</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12989,10 +12985,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120054977</v>
+        <v>120054971</v>
       </c>
       <c r="B115" t="n">
-        <v>95478</v>
+        <v>78278</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13005,21 +13001,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13029,13 +13025,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>411907</v>
+        <v>411826</v>
       </c>
       <c r="R115" t="n">
-        <v>6707588</v>
+        <v>6707438</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13091,10 +13087,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120054967</v>
+        <v>120054969</v>
       </c>
       <c r="B116" t="n">
-        <v>91839</v>
+        <v>79495</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13103,41 +13099,44 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6055</v>
+        <v>391</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Grynig gelélav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Collema subflaccidum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Bäckelberget, Vrm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>411713</v>
+        <v>411805</v>
       </c>
       <c r="R116" t="n">
-        <v>6707349</v>
+        <v>6707377</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13175,6 +13174,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13193,10 +13193,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120054973</v>
+        <v>120054975</v>
       </c>
       <c r="B117" t="n">
-        <v>92048</v>
+        <v>78278</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13209,21 +13209,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13233,10 +13233,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>411943</v>
+        <v>411903</v>
       </c>
       <c r="R117" t="n">
-        <v>6707401</v>
+        <v>6707549</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120054965</v>
+        <v>120054972</v>
       </c>
       <c r="B118" t="n">
-        <v>78278</v>
+        <v>95478</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13311,21 +13311,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13335,13 +13335,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>411707</v>
+        <v>411913</v>
       </c>
       <c r="R118" t="n">
-        <v>6707356</v>
+        <v>6707396</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120054971</v>
+        <v>120054973</v>
       </c>
       <c r="B119" t="n">
-        <v>78278</v>
+        <v>92048</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13413,21 +13413,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13437,10 +13437,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>411826</v>
+        <v>411943</v>
       </c>
       <c r="R119" t="n">
-        <v>6707438</v>
+        <v>6707401</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13499,10 +13499,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120054974</v>
+        <v>120054967</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13511,25 +13511,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13539,10 +13539,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>411945</v>
+        <v>411713</v>
       </c>
       <c r="R120" t="n">
-        <v>6707435</v>
+        <v>6707349</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120054964</v>
+        <v>120054966</v>
       </c>
       <c r="B121" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13613,25 +13613,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13641,10 +13641,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>411669</v>
+        <v>411714</v>
       </c>
       <c r="R121" t="n">
-        <v>6707329</v>
+        <v>6707352</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12988,7 +12988,7 @@
         <v>120054969</v>
       </c>
       <c r="B115" t="n">
-        <v>79551</v>
+        <v>79554</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12988,7 +12988,7 @@
         <v>120054969</v>
       </c>
       <c r="B115" t="n">
-        <v>79554</v>
+        <v>79557</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12988,7 +12988,7 @@
         <v>120054969</v>
       </c>
       <c r="B115" t="n">
-        <v>79557</v>
+        <v>79560</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12988,7 +12988,7 @@
         <v>120054969</v>
       </c>
       <c r="B115" t="n">
-        <v>79560</v>
+        <v>79561</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -12988,7 +12988,7 @@
         <v>120054969</v>
       </c>
       <c r="B115" t="n">
-        <v>79561</v>
+        <v>79495</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13072,28 +13072,9 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>stereolupp</t>
-        </is>
-      </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY121"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13701,6 +13701,147 @@
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>125263204</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Bäckelberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>411957</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6707404</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Hona sågs besöka bo med föda åt ungar.</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Samuel Holdar, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Samuel Holdar, Elliot Örjes</t>
+          <t>Samuel Holdar, Elliot Örjes, Andreas Holmblad Skymberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13706,7 +13706,7 @@
         <v>125263204</v>
       </c>
       <c r="B122" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Samuel Holdar, Elliot Örjes, Andreas Holmblad Skymberg</t>
+          <t>Elliot Örjes, Samuel Holdar, Andreas Holmblad Skymberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13706,12 +13706,7 @@
         <v>125263204</v>
       </c>
       <c r="B122" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13837,7 +13832,7 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Elliot Örjes, Samuel Holdar, Andreas Holmblad Skymberg</t>
+          <t>Samuel Holdar, Elliot Örjes, Andreas Holmblad Skymberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13837,6 +13837,220 @@
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128053984</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92625</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Bäckelbergstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>411788</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6707238</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Hannah Bodin</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Hannah Bodin</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128053978</v>
+      </c>
+      <c r="B124" t="n">
+        <v>92625</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Bäckelbergstjärnen, Bäckelbergstjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>411785</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6707237</v>
+      </c>
+      <c r="S124" t="n">
+        <v>3</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Jon Eklund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14051,6 +14051,976 @@
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128646642</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>411850</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6707387</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128646617</v>
+      </c>
+      <c r="B126" t="n">
+        <v>75171</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>411903</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6707587</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128646634</v>
+      </c>
+      <c r="B127" t="n">
+        <v>81068</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>411783</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6707329</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128646627</v>
+      </c>
+      <c r="B128" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>411752</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6707112</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128646640</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>411755</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6707287</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128646648</v>
+      </c>
+      <c r="B130" t="n">
+        <v>92743</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>411753</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6707281</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128646649</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92743</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>411660</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6707286</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128646638</v>
+      </c>
+      <c r="B132" t="n">
+        <v>78840</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>411754</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6707115</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128646628</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92779</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>411682</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6707393</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128646629</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92779</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Nattjärnsskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>411746</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6707119</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81068</v>
+        <v>81072</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91872</v>
+        <v>91877</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14538,10 +14538,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128646648</v>
+        <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14573,10 +14573,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>411753</v>
+        <v>411660</v>
       </c>
       <c r="R130" t="n">
-        <v>6707281</v>
+        <v>6707286</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14635,10 +14635,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128646649</v>
+        <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14670,10 +14670,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>411660</v>
+        <v>411753</v>
       </c>
       <c r="R131" t="n">
-        <v>6707286</v>
+        <v>6707281</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92779</v>
+        <v>92784</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92779</v>
+        <v>92784</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -13842,7 +13842,7 @@
         <v>128053984</v>
       </c>
       <c r="B123" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>128053978</v>
       </c>
       <c r="B124" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91877</v>
+        <v>91883</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81072</v>
+        <v>81074</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91883</v>
+        <v>91885</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81074</v>
+        <v>81101</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91886</v>
+        <v>91913</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81101</v>
+        <v>81105</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91913</v>
+        <v>91918</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91918</v>
+        <v>91923</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81105</v>
+        <v>81109</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91923</v>
+        <v>91927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81109</v>
+        <v>81014</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81014</v>
+        <v>81019</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91935</v>
+        <v>91940</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78786</v>
+        <v>78791</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81019</v>
+        <v>81020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -14056,7 +14056,7 @@
         <v>128646642</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>128646617</v>
       </c>
       <c r="B126" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>128646634</v>
       </c>
       <c r="B127" t="n">
-        <v>81020</v>
+        <v>81024</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>128646627</v>
       </c>
       <c r="B128" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>128646640</v>
       </c>
       <c r="B129" t="n">
-        <v>91946</v>
+        <v>91953</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>128646649</v>
       </c>
       <c r="B130" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>128646648</v>
       </c>
       <c r="B131" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>128646638</v>
       </c>
       <c r="B132" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>128646628</v>
       </c>
       <c r="B133" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>128646629</v>
       </c>
       <c r="B134" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -15026,7 +15026,7 @@
         <v>134237440</v>
       </c>
       <c r="B135" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 18304-2024 artfynd.xlsx
+++ b/artfynd/A 18304-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY151"/>
+  <dimension ref="A1:AZ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7129039</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117768757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054972</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054977</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495311</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117773996</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495320</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7129037</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108976179</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495318</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495330</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1858,6 +1918,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020832</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1959,6 +2024,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020897</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259211</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495313</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646634</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259300</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2452,6 +2542,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495317</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020723</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2665,6 +2765,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646622</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2762,6 +2867,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495322</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2859,6 +2969,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495332</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2956,6 +3071,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054973</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3072,6 +3192,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/727265</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3182,6 +3307,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81958830</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3288,6 +3418,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124716278</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3389,6 +3524,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108975952</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3490,6 +3630,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259279</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3591,6 +3736,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259323</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3692,6 +3842,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486557</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3789,6 +3944,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935891</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3896,6 +4056,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128053978</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4003,6 +4168,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128053984</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4104,6 +4274,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108976282</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4201,6 +4376,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054964</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4298,6 +4478,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054974</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4395,6 +4580,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646648</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4492,6 +4682,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646649</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4589,6 +4784,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646623</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4696,6 +4896,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117768740</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4793,6 +4998,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646640</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4894,6 +5104,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259079</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5003,6 +5218,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117368459</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5100,6 +5320,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495321</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5202,6 +5427,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119935734</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5300,6 +5530,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957135</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5397,6 +5632,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054980</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5494,6 +5734,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646628</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5591,6 +5836,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646629</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5688,6 +5938,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054967</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5789,6 +6044,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108976119</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5890,6 +6150,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111967347</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5991,6 +6256,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259183</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6092,6 +6362,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259250</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6193,6 +6468,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486584</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6294,6 +6574,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486750</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6395,6 +6680,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486966</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6519,6 +6809,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490129</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6620,6 +6915,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490653</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6717,6 +7017,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495335</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6818,6 +7123,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020889</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6915,6 +7225,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054976</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7012,6 +7327,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646642</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7109,6 +7429,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134237440</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7210,6 +7535,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259138</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7311,6 +7641,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486801</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7412,6 +7747,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108976008</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7513,6 +7853,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259246</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7614,6 +7959,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486520</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7715,6 +8065,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486743</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7812,6 +8167,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646617</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7913,6 +8273,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108975986</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8014,6 +8379,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259116</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8115,6 +8485,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486620</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8216,6 +8591,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486654</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8317,6 +8697,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486703</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8418,6 +8803,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486804</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8519,6 +8909,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486862</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8620,6 +9015,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486929</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8721,6 +9121,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490354</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8822,6 +9227,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490743</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8923,6 +9333,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490812</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9020,6 +9435,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495314</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9117,6 +9537,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495325</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9218,6 +9643,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020753</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9315,6 +9745,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054965</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9412,6 +9847,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054971</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9509,6 +9949,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054975</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9606,6 +10051,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646638</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9703,6 +10153,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495333</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9800,6 +10255,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7129038</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9901,6 +10361,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108975993</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10002,6 +10467,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259103</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10103,6 +10573,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486612</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10204,6 +10679,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486636</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10305,6 +10785,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486858</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10402,6 +10887,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495324</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10503,6 +10993,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020748</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10604,6 +11099,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259394</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10705,6 +11205,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020735</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10819,6 +11324,11 @@
       <c r="AY102" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1872680</t>
         </is>
       </c>
     </row>
@@ -10927,6 +11437,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81958685</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11033,6 +11548,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968648</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11161,6 +11681,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490395</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11262,6 +11787,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020733</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11383,6 +11913,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124716259</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11493,6 +12028,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133658313</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11594,6 +12134,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968649</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11710,6 +12255,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490477</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11822,6 +12372,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119387355</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11932,6 +12487,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104010166</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12037,6 +12597,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259258</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12142,6 +12707,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259378</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12247,6 +12817,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117487095</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12357,6 +12932,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495315</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12493,6 +13073,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125263204</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12632,6 +13217,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64891994</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12739,6 +13329,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259343</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12856,6 +13451,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64892136</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12961,6 +13561,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259223</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13080,6 +13685,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490236</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13177,6 +13787,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134239284</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13279,6 +13894,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968650</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13386,6 +14006,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117763336</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13484,6 +14109,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93088717</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13585,6 +14215,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108975982</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13686,6 +14321,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259147</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13787,6 +14427,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117368504</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13888,6 +14533,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486531</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13989,6 +14639,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486616</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14090,6 +14745,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486800</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14191,6 +14851,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486832</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14292,6 +14957,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486865</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14393,6 +15063,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486935</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14494,6 +15169,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117486983</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14595,6 +15275,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490696</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14696,6 +15381,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490817</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14793,6 +15483,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495323</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14890,6 +15585,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117495329</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14991,6 +15691,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020795</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15088,6 +15793,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120054966</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15185,6 +15895,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646627</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15286,6 +16001,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115259355</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15387,6 +16107,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117368432</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15503,6 +16228,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117490620</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15604,6 +16334,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120020731</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15701,6 +16436,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646636</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15807,6 +16547,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115813460</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15928,6 +16673,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115968638</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16049,8 +16799,165 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124716294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>